--- a/data/Data estacional.xlsx
+++ b/data/Data estacional.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\econometria-udep\econometria-app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E7A217F-BED6-4F5F-8956-850FEF0B2ED8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45A3CBEB-CF08-4943-B1E4-D492AC6E30A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="16080" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
+    <sheet name="Hoja2" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Hoja1!$A$1:$D$253</definedName>
@@ -134,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -145,6 +146,7 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3898,12 +3900,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M253"/>
+  <dimension ref="A1:M219"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" customWidth="1"/>
     <col min="2" max="2" width="19.140625" customWidth="1"/>
-    <col min="9" max="9" width="23" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" customWidth="1"/>
     <col min="10" max="10" width="18.28515625" customWidth="1"/>
     <col min="11" max="11" width="19.5703125" customWidth="1"/>
     <col min="13" max="13" width="25.5703125" customWidth="1"/>
@@ -3975,13 +3977,13 @@
       <c r="H2">
         <v>423.84500000000003</v>
       </c>
-      <c r="I2">
-        <v>7.3503285399143595E-2</v>
+      <c r="I2" s="4">
+        <v>7.3503285399143553E-2</v>
       </c>
       <c r="J2">
         <v>803.90099999999995</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="4">
         <v>5.7339149969958987E-2</v>
       </c>
       <c r="L2">
@@ -4016,14 +4018,14 @@
       <c r="H3">
         <v>429.81599999999997</v>
       </c>
-      <c r="I3">
-        <v>7.4023393546291449E-2</v>
+      <c r="I3" s="4">
+        <v>7.4325548105257114E-2</v>
       </c>
       <c r="J3">
         <v>815.74099999999999</v>
       </c>
-      <c r="K3">
-        <v>5.7207578214369927E-2</v>
+      <c r="K3" s="4">
+        <v>5.7396811446027707E-2</v>
       </c>
       <c r="L3">
         <v>3.5</v>
@@ -4057,14 +4059,14 @@
       <c r="H4">
         <v>445.13900000000001</v>
       </c>
-      <c r="I4">
-        <v>7.6362555035765653E-2</v>
+      <c r="I4" s="4">
+        <v>7.7040629968236699E-2</v>
       </c>
       <c r="J4">
         <v>839.89200000000005</v>
       </c>
-      <c r="K4">
-        <v>5.9231655938548573E-2</v>
+      <c r="K4" s="4">
+        <v>5.9869081755233089E-2</v>
       </c>
       <c r="L4">
         <v>3</v>
@@ -4098,14 +4100,14 @@
       <c r="H5">
         <v>456.49599999999998</v>
       </c>
-      <c r="I5">
-        <v>7.3923348040563136E-2</v>
+      <c r="I5" s="4">
+        <v>7.4539014847396667E-2</v>
       </c>
       <c r="J5">
         <v>861.851</v>
       </c>
-      <c r="K5">
-        <v>5.6902517788027761E-2</v>
+      <c r="K5" s="4">
+        <v>5.749019747812037E-2</v>
       </c>
       <c r="L5">
         <v>3</v>
@@ -4139,14 +4141,14 @@
       <c r="H6">
         <v>471.23599999999999</v>
       </c>
-      <c r="I6">
-        <v>7.2218557598468902E-2</v>
+      <c r="I6" s="4">
+        <v>7.2717692183490501E-2</v>
       </c>
       <c r="J6">
         <v>892.58999999999992</v>
       </c>
-      <c r="K6">
-        <v>5.584307338801648E-2</v>
+      <c r="K6" s="4">
+        <v>5.6376964144713541E-2</v>
       </c>
       <c r="L6">
         <v>3</v>
@@ -4180,14 +4182,14 @@
       <c r="H7">
         <v>483.49799999999999</v>
       </c>
-      <c r="I7">
-        <v>7.2273461171468351E-2</v>
+      <c r="I7" s="4">
+        <v>7.26906979430577E-2</v>
       </c>
       <c r="J7">
         <v>920.5630000000001</v>
       </c>
-      <c r="K7">
-        <v>5.5352034549793393E-2</v>
+      <c r="K7" s="4">
+        <v>5.5848400063943142E-2</v>
       </c>
       <c r="L7">
         <v>3</v>
@@ -4221,14 +4223,14 @@
       <c r="H8">
         <v>502.80700000000002</v>
       </c>
-      <c r="I8">
-        <v>6.8053104704699274E-2</v>
+      <c r="I8" s="4">
+        <v>6.8242226118145191E-2</v>
       </c>
       <c r="J8">
         <v>955.93200000000002</v>
       </c>
-      <c r="K8">
-        <v>5.2880499407597648E-2</v>
+      <c r="K8" s="4">
+        <v>5.3237615491503562E-2</v>
       </c>
       <c r="L8">
         <v>3.25</v>
@@ -4262,14 +4264,14 @@
       <c r="H9">
         <v>520.96699999999998</v>
       </c>
-      <c r="I9">
-        <v>6.4814751285861408E-2</v>
+      <c r="I9" s="4">
+        <v>6.4766648285196696E-2</v>
       </c>
       <c r="J9">
         <v>1003.971</v>
       </c>
-      <c r="K9">
-        <v>4.9629812054326712E-2</v>
+      <c r="K9" s="4">
+        <v>4.9780122480453687E-2</v>
       </c>
       <c r="L9">
         <v>3.25</v>
@@ -4303,14 +4305,14 @@
       <c r="H10">
         <v>538.88900000000001</v>
       </c>
-      <c r="I10">
-        <v>6.4180529390678559E-2</v>
+      <c r="I10" s="4">
+        <v>6.4107226829852884E-2</v>
       </c>
       <c r="J10">
         <v>1052.442</v>
       </c>
-      <c r="K10">
-        <v>4.8844747113439953E-2</v>
+      <c r="K10" s="4">
+        <v>4.9013639252348723E-2</v>
       </c>
       <c r="L10">
         <v>3.75</v>
@@ -4344,14 +4346,14 @@
       <c r="H11">
         <v>560.404</v>
       </c>
-      <c r="I11">
-        <v>6.4025358702307647E-2</v>
+      <c r="I11" s="4">
+        <v>6.3884774390780941E-2</v>
       </c>
       <c r="J11">
         <v>1107.1030000000001</v>
       </c>
-      <c r="K11">
-        <v>4.6537077827255302E-2</v>
+      <c r="K11" s="4">
+        <v>4.665695766451193E-2</v>
       </c>
       <c r="L11">
         <v>4.75</v>
@@ -4385,14 +4387,14 @@
       <c r="H12">
         <v>577.70699999999999</v>
       </c>
-      <c r="I12">
-        <v>6.3271307814498703E-2</v>
+      <c r="I12" s="4">
+        <v>6.3356344302442621E-2</v>
       </c>
       <c r="J12">
         <v>1146.173</v>
       </c>
-      <c r="K12">
-        <v>4.6557953971036001E-2</v>
+      <c r="K12" s="4">
+        <v>4.6752367881576287E-2</v>
       </c>
       <c r="L12">
         <v>4.75</v>
@@ -4426,14 +4428,14 @@
       <c r="H13">
         <v>593.23599999999999</v>
       </c>
-      <c r="I13">
-        <v>6.3245363725760992E-2</v>
+      <c r="I13" s="4">
+        <v>6.3383344366501546E-2</v>
       </c>
       <c r="J13">
         <v>1184.2249999999999</v>
       </c>
-      <c r="K13">
-        <v>4.6923570223188153E-2</v>
+      <c r="K13" s="4">
+        <v>4.7055651919080677E-2</v>
       </c>
       <c r="L13">
         <v>4.5</v>
@@ -4467,13 +4469,13 @@
       <c r="H14">
         <v>589.798</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="4">
         <v>6.1671962265046683E-2</v>
       </c>
       <c r="J14">
         <v>1194.989</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="4">
         <v>4.6478252101065369E-2</v>
       </c>
       <c r="L14">
@@ -4508,14 +4510,14 @@
       <c r="H15">
         <v>604.05600000000004</v>
       </c>
-      <c r="I15">
-        <v>6.0707435702329907E-2</v>
+      <c r="I15" s="4">
+        <v>6.1009590261295571E-2</v>
       </c>
       <c r="J15">
         <v>1230.4649999999999</v>
       </c>
-      <c r="K15">
-        <v>4.4832856496253973E-2</v>
+      <c r="K15" s="4">
+        <v>4.5022089727911753E-2</v>
       </c>
       <c r="L15">
         <v>4.25</v>
@@ -4549,14 +4551,14 @@
       <c r="H16">
         <v>626.01</v>
       </c>
-      <c r="I16">
-        <v>6.2556957650365355E-2</v>
+      <c r="I16" s="4">
+        <v>6.3235032582836401E-2</v>
       </c>
       <c r="J16">
         <v>1272.1199999999999</v>
       </c>
-      <c r="K16">
-        <v>4.6073765704272358E-2</v>
+      <c r="K16" s="4">
+        <v>4.6711191520956867E-2</v>
       </c>
       <c r="L16">
         <v>4.25</v>
@@ -4590,14 +4592,14 @@
       <c r="H17">
         <v>638.35299999999995</v>
       </c>
-      <c r="I17">
-        <v>6.2617139049517892E-2</v>
+      <c r="I17" s="4">
+        <v>6.3232805856351423E-2</v>
       </c>
       <c r="J17">
         <v>1296.5440000000001</v>
       </c>
-      <c r="K17">
-        <v>4.6243335815670999E-2</v>
+      <c r="K17" s="4">
+        <v>4.6831015505763608E-2</v>
       </c>
       <c r="L17">
         <v>4.25</v>
@@ -4631,14 +4633,14 @@
       <c r="H18">
         <v>655.45899999999995</v>
       </c>
-      <c r="I18">
-        <v>6.3083962046870057E-2</v>
+      <c r="I18" s="4">
+        <v>6.3583096631891656E-2</v>
       </c>
       <c r="J18">
         <v>1326.8409999999999</v>
       </c>
-      <c r="K18">
-        <v>4.6756784138373621E-2</v>
+      <c r="K18" s="4">
+        <v>4.7290674895070682E-2</v>
       </c>
       <c r="L18">
         <v>4.25</v>
@@ -4672,14 +4674,14 @@
       <c r="H19">
         <v>667.43100000000004</v>
       </c>
-      <c r="I19">
-        <v>6.4311974918811313E-2</v>
+      <c r="I19" s="4">
+        <v>6.4729211690400662E-2</v>
       </c>
       <c r="J19">
         <v>1349.962</v>
       </c>
-      <c r="K19">
-        <v>4.8527234106591759E-2</v>
+      <c r="K19" s="4">
+        <v>4.9023599620741508E-2</v>
       </c>
       <c r="L19">
         <v>4.25</v>
@@ -4713,14 +4715,14 @@
       <c r="H20">
         <v>683.72900000000004</v>
       </c>
-      <c r="I20">
-        <v>6.2816185679694894E-2</v>
+      <c r="I20" s="4">
+        <v>6.3005307093140811E-2</v>
       </c>
       <c r="J20">
         <v>1378.318</v>
       </c>
-      <c r="K20">
-        <v>4.7070773949618783E-2</v>
+      <c r="K20" s="4">
+        <v>4.7427890033524683E-2</v>
       </c>
       <c r="L20">
         <v>4</v>
@@ -4754,14 +4756,14 @@
       <c r="H21">
         <v>702.43100000000004</v>
       </c>
-      <c r="I21">
-        <v>6.4242554225547394E-2</v>
+      <c r="I21" s="4">
+        <v>6.4194451224882682E-2</v>
       </c>
       <c r="J21">
         <v>1419.5039999999999</v>
       </c>
-      <c r="K21">
-        <v>4.8008485985835028E-2</v>
+      <c r="K21" s="4">
+        <v>4.815879641196201E-2</v>
       </c>
       <c r="L21">
         <v>3.5</v>
@@ -4795,14 +4797,14 @@
       <c r="H22">
         <v>722.02599999999995</v>
       </c>
-      <c r="I22">
-        <v>6.6632851527794301E-2</v>
+      <c r="I22" s="4">
+        <v>6.6559548966968626E-2</v>
       </c>
       <c r="J22">
         <v>1464.114</v>
       </c>
-      <c r="K22">
-        <v>4.9279051979876261E-2</v>
+      <c r="K22" s="4">
+        <v>4.9447944118785038E-2</v>
       </c>
       <c r="L22">
         <v>2.75</v>
@@ -4836,14 +4838,14 @@
       <c r="H23">
         <v>756.31000000000006</v>
       </c>
-      <c r="I23">
-        <v>6.4134914278009561E-2</v>
+      <c r="I23" s="4">
+        <v>6.3994329966482855E-2</v>
       </c>
       <c r="J23">
         <v>1515.5429999999999</v>
       </c>
-      <c r="K23">
-        <v>4.818015636065958E-2</v>
+      <c r="K23" s="4">
+        <v>4.8300036197916223E-2</v>
       </c>
       <c r="L23">
         <v>2.75</v>
@@ -4877,14 +4879,14 @@
       <c r="H24">
         <v>805.49299999999994</v>
       </c>
-      <c r="I24">
-        <v>6.2249736113770583E-2</v>
+      <c r="I24" s="4">
+        <v>6.2334772601714487E-2</v>
       </c>
       <c r="J24">
         <v>1580.4380000000001</v>
       </c>
-      <c r="K24">
-        <v>4.8057934781128443E-2</v>
+      <c r="K24" s="4">
+        <v>4.825234869166873E-2</v>
       </c>
       <c r="L24">
         <v>2.5</v>
@@ -4918,14 +4920,14 @@
       <c r="H25">
         <v>830.68899999999996</v>
       </c>
-      <c r="I25">
-        <v>6.4047499261083302E-2</v>
+      <c r="I25" s="4">
+        <v>6.4185479901823855E-2</v>
       </c>
       <c r="J25">
         <v>1623.732</v>
       </c>
-      <c r="K25">
-        <v>4.8848921675328158E-2</v>
+      <c r="K25" s="4">
+        <v>4.8981003371220688E-2</v>
       </c>
       <c r="L25">
         <v>2.5</v>
@@ -4959,13 +4961,13 @@
       <c r="H26">
         <v>836.94200000000001</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="4">
         <v>6.3791756179042272E-2</v>
       </c>
       <c r="J26">
         <v>1641.6690000000001</v>
       </c>
-      <c r="K26">
+      <c r="K26" s="4">
         <v>4.7681962685535283E-2</v>
       </c>
       <c r="L26">
@@ -5000,14 +5002,14 @@
       <c r="H27">
         <v>854.36400000000003</v>
       </c>
-      <c r="I27">
-        <v>6.4925059561367557E-2</v>
+      <c r="I27" s="4">
+        <v>6.5227214120333221E-2</v>
       </c>
       <c r="J27">
         <v>1672.02</v>
       </c>
-      <c r="K27">
-        <v>4.8661745050178958E-2</v>
+      <c r="K27" s="4">
+        <v>4.8850978281836752E-2</v>
       </c>
       <c r="L27">
         <v>2.5</v>
@@ -5041,14 +5043,14 @@
       <c r="H28">
         <v>891.87099999999998</v>
       </c>
-      <c r="I28">
-        <v>6.5510244126873785E-2</v>
+      <c r="I28" s="4">
+        <v>6.618831905934483E-2</v>
       </c>
       <c r="J28">
         <v>1725.3879999999999</v>
       </c>
-      <c r="K28">
-        <v>4.9129791261555943E-2</v>
+      <c r="K28" s="4">
+        <v>4.9767217078240458E-2</v>
       </c>
       <c r="L28">
         <v>2.5</v>
@@ -5082,14 +5084,14 @@
       <c r="H29">
         <v>913.06500000000005</v>
       </c>
-      <c r="I29">
-        <v>6.6970178431669289E-2</v>
+      <c r="I29" s="4">
+        <v>6.758584523850282E-2</v>
       </c>
       <c r="J29">
         <v>1756.796</v>
       </c>
-      <c r="K29">
-        <v>4.972872566219555E-2</v>
+      <c r="K29" s="4">
+        <v>5.0316405352288159E-2</v>
       </c>
       <c r="L29">
         <v>2.5</v>
@@ -5123,14 +5125,14 @@
       <c r="H30">
         <v>932.97</v>
       </c>
-      <c r="I30">
-        <v>6.617392280524248E-2</v>
+      <c r="I30" s="4">
+        <v>6.6673057390264079E-2</v>
       </c>
       <c r="J30">
         <v>1775.136</v>
       </c>
-      <c r="K30">
-        <v>5.0087578632937148E-2</v>
+      <c r="K30" s="4">
+        <v>5.0621469389634209E-2</v>
       </c>
       <c r="L30">
         <v>2.5</v>
@@ -5164,14 +5166,14 @@
       <c r="H31">
         <v>949.41100000000006</v>
       </c>
-      <c r="I31">
-        <v>7.2916375774342929E-2</v>
+      <c r="I31" s="4">
+        <v>7.3333612545932278E-2</v>
       </c>
       <c r="J31">
         <v>1798.509</v>
       </c>
-      <c r="K31">
-        <v>5.4319454875439308E-2</v>
+      <c r="K31" s="4">
+        <v>5.4815820389589057E-2</v>
       </c>
       <c r="L31">
         <v>2.5</v>
@@ -5205,14 +5207,14 @@
       <c r="H32">
         <v>961.62199999999996</v>
       </c>
-      <c r="I32">
-        <v>7.4933294438158132E-2</v>
+      <c r="I32" s="4">
+        <v>7.5122415851604049E-2</v>
       </c>
       <c r="J32">
         <v>1806.241</v>
       </c>
-      <c r="K32">
-        <v>5.5986053069720203E-2</v>
+      <c r="K32" s="4">
+        <v>5.6343169153626103E-2</v>
       </c>
       <c r="L32">
         <v>2.5</v>
@@ -5246,14 +5248,14 @@
       <c r="H33">
         <v>980.64400000000001</v>
       </c>
-      <c r="I33">
-        <v>7.4002394855385914E-2</v>
+      <c r="I33" s="4">
+        <v>7.3954291854721202E-2</v>
       </c>
       <c r="J33">
         <v>1832.4179999999999</v>
       </c>
-      <c r="K33">
-        <v>5.5628072948071518E-2</v>
+      <c r="K33" s="4">
+        <v>5.5778383374198513E-2</v>
       </c>
       <c r="L33">
         <v>2.75</v>
@@ -5287,14 +5289,14 @@
       <c r="H34">
         <v>1007.597</v>
       </c>
-      <c r="I34">
-        <v>7.2065425608790437E-2</v>
+      <c r="I34" s="4">
+        <v>7.1992123047964762E-2</v>
       </c>
       <c r="J34">
         <v>1878.732</v>
       </c>
-      <c r="K34">
-        <v>5.4229400220562329E-2</v>
+      <c r="K34" s="4">
+        <v>5.4398292359471113E-2</v>
       </c>
       <c r="L34">
         <v>2.75</v>
@@ -5328,14 +5330,14 @@
       <c r="H35">
         <v>1024.7460000000001</v>
       </c>
-      <c r="I35">
-        <v>6.9629179876902036E-2</v>
+      <c r="I35" s="4">
+        <v>6.948859556537533E-2</v>
       </c>
       <c r="J35">
         <v>1915.915</v>
       </c>
-      <c r="K35">
-        <v>5.3503870818863791E-2</v>
+      <c r="K35" s="4">
+        <v>5.3623750656120427E-2</v>
       </c>
       <c r="L35">
         <v>3</v>
@@ -5369,14 +5371,14 @@
       <c r="H36">
         <v>1069.412</v>
       </c>
-      <c r="I36">
-        <v>6.9215393368752945E-2</v>
+      <c r="I36" s="4">
+        <v>6.9300429856696863E-2</v>
       </c>
       <c r="J36">
         <v>1992.28</v>
       </c>
-      <c r="K36">
-        <v>5.2555343021155831E-2</v>
+      <c r="K36" s="4">
+        <v>5.2749756931696118E-2</v>
       </c>
       <c r="L36">
         <v>3</v>
@@ -5410,14 +5412,14 @@
       <c r="H37">
         <v>1111.04079688</v>
       </c>
-      <c r="I37">
-        <v>7.4306494426438247E-2</v>
+      <c r="I37" s="4">
+        <v>7.44444750671788E-2</v>
       </c>
       <c r="J37">
         <v>2066.3907967099999</v>
       </c>
-      <c r="K37">
-        <v>5.5504015326721598E-2</v>
+      <c r="K37" s="4">
+        <v>5.5636097022614121E-2</v>
       </c>
       <c r="L37">
         <v>3</v>
@@ -5451,13 +5453,13 @@
       <c r="H38">
         <v>1098.5709999999999</v>
       </c>
-      <c r="I38">
+      <c r="I38" s="4">
         <v>7.8030459569750174E-2</v>
       </c>
       <c r="J38">
         <v>2064.0050000000001</v>
       </c>
-      <c r="K38">
+      <c r="K38" s="4">
         <v>5.7845305607302312E-2</v>
       </c>
       <c r="L38">
@@ -5492,14 +5494,14 @@
       <c r="H39">
         <v>1118.2339999999999</v>
       </c>
-      <c r="I39">
-        <v>7.7638389350231818E-2</v>
+      <c r="I39" s="4">
+        <v>7.7940543909197482E-2</v>
       </c>
       <c r="J39">
         <v>2100.4059999999999</v>
       </c>
-      <c r="K39">
-        <v>5.7065152161425693E-2</v>
+      <c r="K39" s="4">
+        <v>5.725438539308348E-2</v>
       </c>
       <c r="L39">
         <v>3</v>
@@ -5533,14 +5535,14 @@
       <c r="H40">
         <v>1141.2049999999999</v>
       </c>
-      <c r="I40">
-        <v>7.6911537444997347E-2</v>
+      <c r="I40" s="4">
+        <v>7.7589612377468392E-2</v>
       </c>
       <c r="J40">
         <v>2149.7139999999999</v>
       </c>
-      <c r="K40">
-        <v>5.6083845500933087E-2</v>
+      <c r="K40" s="4">
+        <v>5.6721271317617609E-2</v>
       </c>
       <c r="L40">
         <v>3</v>
@@ -5574,14 +5576,14 @@
       <c r="H41">
         <v>1168.1579999999999</v>
       </c>
-      <c r="I41">
-        <v>7.6296938745110732E-2</v>
+      <c r="I41" s="4">
+        <v>7.6912605551944263E-2</v>
       </c>
       <c r="J41">
         <v>2191.56</v>
       </c>
-      <c r="K41">
-        <v>5.536515609713967E-2</v>
+      <c r="K41" s="4">
+        <v>5.5952835787232279E-2</v>
       </c>
       <c r="L41">
         <v>3</v>
@@ -5615,14 +5617,14 @@
       <c r="H42">
         <v>1182.146</v>
       </c>
-      <c r="I42">
-        <v>7.6561460538960333E-2</v>
+      <c r="I42" s="4">
+        <v>7.7060595123981931E-2</v>
       </c>
       <c r="J42">
         <v>2218.1990000000001</v>
       </c>
-      <c r="K42">
-        <v>5.5616519042282472E-2</v>
+      <c r="K42" s="4">
+        <v>5.6150409798979527E-2</v>
       </c>
       <c r="L42">
         <v>3</v>
@@ -5656,14 +5658,14 @@
       <c r="H43">
         <v>1191.4269999999999</v>
       </c>
-      <c r="I43">
-        <v>7.4718270482840451E-2</v>
+      <c r="I43" s="4">
+        <v>7.5135507254429801E-2</v>
       </c>
       <c r="J43">
         <v>2253.0819999999999</v>
       </c>
-      <c r="K43">
-        <v>5.4313521953647761E-2</v>
+      <c r="K43" s="4">
+        <v>5.4809887467797511E-2</v>
       </c>
       <c r="L43">
         <v>3</v>
@@ -5697,14 +5699,14 @@
       <c r="H44">
         <v>1208.9159999999999</v>
       </c>
-      <c r="I44">
-        <v>7.5939385399945741E-2</v>
+      <c r="I44" s="4">
+        <v>7.6128506813391658E-2</v>
       </c>
       <c r="J44">
         <v>2299.2640000000001</v>
       </c>
-      <c r="K44">
-        <v>5.4306120976639748E-2</v>
+      <c r="K44" s="4">
+        <v>5.4663237060545662E-2</v>
       </c>
       <c r="L44">
         <v>3</v>
@@ -5738,14 +5740,14 @@
       <c r="H45">
         <v>1234.9349999999999</v>
       </c>
-      <c r="I45">
-        <v>7.3131871844574994E-2</v>
+      <c r="I45" s="4">
+        <v>7.3083768843910282E-2</v>
       </c>
       <c r="J45">
         <v>2361.2910000000002</v>
       </c>
-      <c r="K45">
-        <v>5.3059081995063651E-2</v>
+      <c r="K45" s="4">
+        <v>5.3209392421190632E-2</v>
       </c>
       <c r="L45">
         <v>3</v>
@@ -5779,14 +5781,14 @@
       <c r="H46">
         <v>1272.1969999999999</v>
       </c>
-      <c r="I46">
-        <v>7.3067740929524991E-2</v>
+      <c r="I46" s="4">
+        <v>7.2994438368699316E-2</v>
       </c>
       <c r="J46">
         <v>2441.98</v>
       </c>
-      <c r="K46">
-        <v>5.3431388110152918E-2</v>
+      <c r="K46" s="4">
+        <v>5.3600280249061702E-2</v>
       </c>
       <c r="L46">
         <v>3</v>
@@ -5820,14 +5822,14 @@
       <c r="H47">
         <v>1311.17</v>
       </c>
-      <c r="I47">
-        <v>7.2381325195421939E-2</v>
+      <c r="I47" s="4">
+        <v>7.2240740883895233E-2</v>
       </c>
       <c r="J47">
         <v>2514.0650000000001</v>
       </c>
-      <c r="K47">
-        <v>5.3285144679888451E-2</v>
+      <c r="K47" s="4">
+        <v>5.3405024517145093E-2</v>
       </c>
       <c r="L47">
         <v>3</v>
@@ -5861,14 +5863,14 @@
       <c r="H48">
         <v>1365.585</v>
       </c>
-      <c r="I48">
-        <v>6.9655120933660955E-2</v>
+      <c r="I48" s="4">
+        <v>6.9740157421604873E-2</v>
       </c>
       <c r="J48">
         <v>2607.4549999999999</v>
       </c>
-      <c r="K48">
-        <v>5.1153522438219613E-2</v>
+      <c r="K48" s="4">
+        <v>5.1347936348759907E-2</v>
       </c>
       <c r="L48">
         <v>3</v>
@@ -5902,14 +5904,14 @@
       <c r="H49">
         <v>1408.7850000000001</v>
       </c>
-      <c r="I49">
-        <v>6.8213908511132737E-2</v>
+      <c r="I49" s="4">
+        <v>6.8351889151873305E-2</v>
       </c>
       <c r="J49">
         <v>2681.643</v>
       </c>
-      <c r="K49">
-        <v>5.1776300198114772E-2</v>
+      <c r="K49" s="4">
+        <v>5.1908381894007302E-2</v>
       </c>
       <c r="L49">
         <v>3.25</v>
@@ -5943,13 +5945,13 @@
       <c r="H50">
         <v>1393.1179999999999</v>
       </c>
-      <c r="I50">
+      <c r="I50" s="4">
         <v>6.8040180372373346E-2</v>
       </c>
       <c r="J50">
         <v>2663.5709999999999</v>
       </c>
-      <c r="K50">
+      <c r="K50" s="4">
         <v>5.1246991351084688E-2</v>
       </c>
       <c r="L50">
@@ -5984,14 +5986,14 @@
       <c r="H51">
         <v>1424.1969999999999</v>
       </c>
-      <c r="I51">
-        <v>6.7979498569936306E-2</v>
+      <c r="I51" s="4">
+        <v>6.828165312890197E-2</v>
       </c>
       <c r="J51">
         <v>2708.942</v>
       </c>
-      <c r="K51">
-        <v>5.1548718471280917E-2</v>
+      <c r="K51" s="4">
+        <v>5.1737951702938698E-2</v>
       </c>
       <c r="L51">
         <v>3.75</v>
@@ -6025,14 +6027,14 @@
       <c r="H52">
         <v>1472.2570000000001</v>
       </c>
-      <c r="I52">
-        <v>6.5894548784706949E-2</v>
+      <c r="I52" s="4">
+        <v>6.6572623717177995E-2</v>
       </c>
       <c r="J52">
         <v>2783.2559999999999</v>
       </c>
-      <c r="K52">
-        <v>5.0375856078739727E-2</v>
+      <c r="K52" s="4">
+        <v>5.1013281895424249E-2</v>
       </c>
       <c r="L52">
         <v>4</v>
@@ -6066,14 +6068,14 @@
       <c r="H53">
         <v>1478.075</v>
       </c>
-      <c r="I53">
-        <v>6.4897773023878058E-2</v>
+      <c r="I53" s="4">
+        <v>6.5513439830711589E-2</v>
       </c>
       <c r="J53">
         <v>2798.692</v>
       </c>
-      <c r="K53">
-        <v>5.0937152427815442E-2</v>
+      <c r="K53" s="4">
+        <v>5.1524832117908037E-2</v>
       </c>
       <c r="L53">
         <v>4.25</v>
@@ -6107,14 +6109,14 @@
       <c r="H54">
         <v>1498.213</v>
       </c>
-      <c r="I54">
-        <v>6.4779514155196491E-2</v>
+      <c r="I54" s="4">
+        <v>6.527864874021809E-2</v>
       </c>
       <c r="J54">
         <v>2842.3690000000001</v>
       </c>
-      <c r="K54">
-        <v>5.014969082844295E-2</v>
+      <c r="K54" s="4">
+        <v>5.0683581585140011E-2</v>
       </c>
       <c r="L54">
         <v>4.5</v>
@@ -6148,14 +6150,14 @@
       <c r="H55">
         <v>1514.933</v>
       </c>
-      <c r="I55">
-        <v>6.5917532434370721E-2</v>
+      <c r="I55" s="4">
+        <v>6.633476920596007E-2</v>
       </c>
       <c r="J55">
         <v>2867.7020000000002</v>
       </c>
-      <c r="K55">
-        <v>5.0921823522919789E-2</v>
+      <c r="K55" s="4">
+        <v>5.1418189037069538E-2</v>
       </c>
       <c r="L55">
         <v>4.5</v>
@@ -6189,14 +6191,14 @@
       <c r="H56">
         <v>1526.9110000000001</v>
       </c>
-      <c r="I56">
-        <v>6.5807070449670588E-2</v>
+      <c r="I56" s="4">
+        <v>6.5996191863116505E-2</v>
       </c>
       <c r="J56">
         <v>2902.9949999999999</v>
       </c>
-      <c r="K56">
-        <v>5.0680249900343477E-2</v>
+      <c r="K56" s="4">
+        <v>5.1037365984249378E-2</v>
       </c>
       <c r="L56">
         <v>4.5</v>
@@ -6230,14 +6232,14 @@
       <c r="H57">
         <v>1559.5129999999999</v>
       </c>
-      <c r="I57">
-        <v>6.5686320169562995E-2</v>
+      <c r="I57" s="4">
+        <v>6.5638217168898283E-2</v>
       </c>
       <c r="J57">
         <v>2978.0120000000002</v>
       </c>
-      <c r="K57">
-        <v>5.033903837760708E-2</v>
+      <c r="K57" s="4">
+        <v>5.0489348803734062E-2</v>
       </c>
       <c r="L57">
         <v>4.5</v>
@@ -6271,14 +6273,14 @@
       <c r="H58">
         <v>1592.5260000000001</v>
       </c>
-      <c r="I58">
-        <v>6.6582398380599941E-2</v>
+      <c r="I58" s="4">
+        <v>6.6509095819774267E-2</v>
       </c>
       <c r="J58">
         <v>3073.47</v>
       </c>
-      <c r="K58">
-        <v>5.0166657839465563E-2</v>
+      <c r="K58" s="4">
+        <v>5.0335549978374333E-2</v>
       </c>
       <c r="L58">
         <v>4.5</v>
@@ -6312,14 +6314,14 @@
       <c r="H59">
         <v>1639.186864</v>
       </c>
-      <c r="I59">
-        <v>6.6781900313727563E-2</v>
+      <c r="I59" s="4">
+        <v>6.6641316002200857E-2</v>
       </c>
       <c r="J59">
         <v>3154.2887730000002</v>
       </c>
-      <c r="K59">
-        <v>5.0692207135743711E-2</v>
+      <c r="K59" s="4">
+        <v>5.0812086973000353E-2</v>
       </c>
       <c r="L59">
         <v>4.5</v>
@@ -6353,14 +6355,14 @@
       <c r="H60">
         <v>1697.2960840000001</v>
       </c>
-      <c r="I60">
-        <v>6.468420252460684E-2</v>
+      <c r="I60" s="4">
+        <v>6.4769239012550758E-2</v>
       </c>
       <c r="J60">
         <v>3250.7574420000001</v>
       </c>
-      <c r="K60">
-        <v>4.9984235556574282E-2</v>
+      <c r="K60" s="4">
+        <v>5.0178649467114568E-2</v>
       </c>
       <c r="L60">
         <v>4.5</v>
@@ -6394,14 +6396,14 @@
       <c r="H61">
         <v>1715.617872</v>
       </c>
-      <c r="I61">
-        <v>6.398445487651061E-2</v>
+      <c r="I61" s="4">
+        <v>6.4122435517251164E-2</v>
       </c>
       <c r="J61">
         <v>3295.320012000001</v>
       </c>
-      <c r="K61">
-        <v>4.8638965287156943E-2</v>
+      <c r="K61" s="4">
+        <v>4.8771046983049467E-2</v>
       </c>
       <c r="L61">
         <v>4.5</v>
@@ -6435,13 +6437,13 @@
       <c r="H62">
         <v>1690.908555</v>
       </c>
-      <c r="I62">
+      <c r="I62" s="4">
         <v>6.542442089661081E-2</v>
       </c>
       <c r="J62">
         <v>3293.265363</v>
       </c>
-      <c r="K62">
+      <c r="K62" s="4">
         <v>4.9071577048010878E-2</v>
       </c>
       <c r="L62">
@@ -6476,14 +6478,14 @@
       <c r="H63">
         <v>1719.67299</v>
       </c>
-      <c r="I63">
-        <v>6.5220255998563223E-2</v>
+      <c r="I63" s="4">
+        <v>6.5522410557528887E-2</v>
       </c>
       <c r="J63">
         <v>3346.8457210000001</v>
       </c>
-      <c r="K63">
-        <v>4.7948231667899542E-2</v>
+      <c r="K63" s="4">
+        <v>4.8137464899557322E-2</v>
       </c>
       <c r="L63">
         <v>4.5</v>
@@ -6517,14 +6519,14 @@
       <c r="H64">
         <v>1745.3272649999999</v>
       </c>
-      <c r="I64">
-        <v>6.3792199144707781E-2</v>
+      <c r="I64" s="4">
+        <v>6.4470274077178827E-2</v>
       </c>
       <c r="J64">
         <v>3399.4933139999998</v>
       </c>
-      <c r="K64">
-        <v>4.7077294745185523E-2</v>
+      <c r="K64" s="4">
+        <v>4.7714720561870039E-2</v>
       </c>
       <c r="L64">
         <v>4.5</v>
@@ -6558,14 +6560,14 @@
       <c r="H65">
         <v>1760.0811670000001</v>
       </c>
-      <c r="I65">
-        <v>6.343482097958679E-2</v>
+      <c r="I65" s="4">
+        <v>6.4050487786420321E-2</v>
       </c>
       <c r="J65">
         <v>3440.4792269999998</v>
       </c>
-      <c r="K65">
-        <v>4.6630948243938368E-2</v>
+      <c r="K65" s="4">
+        <v>4.7218627934030977E-2</v>
       </c>
       <c r="L65">
         <v>4.5</v>
@@ -6599,14 +6601,14 @@
       <c r="H66">
         <v>1785.299947</v>
       </c>
-      <c r="I66">
-        <v>6.2508796704900935E-2</v>
+      <c r="I66" s="4">
+        <v>6.3007931289922534E-2</v>
       </c>
       <c r="J66">
         <v>3508.5701749999998</v>
       </c>
-      <c r="K66">
-        <v>4.5480187918272567E-2</v>
+      <c r="K66" s="4">
+        <v>4.6014078674969643E-2</v>
       </c>
       <c r="L66">
         <v>4.5</v>
@@ -6640,14 +6642,14 @@
       <c r="H67">
         <v>1802.411325</v>
       </c>
-      <c r="I67">
-        <v>6.1320967440160433E-2</v>
+      <c r="I67" s="4">
+        <v>6.1738204211749782E-2</v>
       </c>
       <c r="J67">
         <v>3545.9625860000001</v>
       </c>
-      <c r="K67">
-        <v>4.4544017829057439E-2</v>
+      <c r="K67" s="4">
+        <v>4.5040383343207188E-2</v>
       </c>
       <c r="L67">
         <v>4.5</v>
@@ -6681,14 +6683,14 @@
       <c r="H68">
         <v>1846.8436380000001</v>
       </c>
-      <c r="I68">
-        <v>5.9886417016612688E-2</v>
+      <c r="I68" s="4">
+        <v>6.0075538430058611E-2</v>
       </c>
       <c r="J68">
         <v>3621.2695960000001</v>
       </c>
-      <c r="K68">
-        <v>4.2953008157174018E-2</v>
+      <c r="K68" s="4">
+        <v>4.3310124241079932E-2</v>
       </c>
       <c r="L68">
         <v>4.75</v>
@@ -6722,14 +6724,14 @@
       <c r="H69">
         <v>1886.026574</v>
       </c>
-      <c r="I69">
-        <v>5.9986570469916331E-2</v>
+      <c r="I69" s="4">
+        <v>5.9938467469251633E-2</v>
       </c>
       <c r="J69">
         <v>3698.937778</v>
       </c>
-      <c r="K69">
-        <v>4.3638536684492753E-2</v>
+      <c r="K69" s="4">
+        <v>4.3788847110619727E-2</v>
       </c>
       <c r="L69">
         <v>4.75</v>
@@ -6763,14 +6765,14 @@
       <c r="H70">
         <v>1924.0648189999999</v>
       </c>
-      <c r="I70">
-        <v>5.9866485225277537E-2</v>
+      <c r="I70" s="4">
+        <v>5.9793182664451869E-2</v>
       </c>
       <c r="J70">
         <v>3766.832343</v>
       </c>
-      <c r="K70">
-        <v>4.3781048190335313E-2</v>
+      <c r="K70" s="4">
+        <v>4.3949940329244083E-2</v>
       </c>
       <c r="L70">
         <v>5</v>
@@ -6804,14 +6806,14 @@
       <c r="H71">
         <v>1976.5700529999999</v>
       </c>
-      <c r="I71">
-        <v>5.906355655465776E-2</v>
+      <c r="I71" s="4">
+        <v>5.8922972243131047E-2</v>
       </c>
       <c r="J71">
         <v>3852.2062299999998</v>
       </c>
-      <c r="K71">
-        <v>4.3047924364368613E-2</v>
+      <c r="K71" s="4">
+        <v>4.3167804201625241E-2</v>
       </c>
       <c r="L71">
         <v>5</v>
@@ -6845,14 +6847,14 @@
       <c r="H72">
         <v>2055.8010490000001</v>
       </c>
-      <c r="I72">
-        <v>5.6369167123607983E-2</v>
+      <c r="I72" s="4">
+        <v>5.6454203611551887E-2</v>
       </c>
       <c r="J72">
         <v>3984.5956160000001</v>
       </c>
-      <c r="K72">
-        <v>4.1782755433823718E-2</v>
+      <c r="K72" s="4">
+        <v>4.1977169344364018E-2</v>
       </c>
       <c r="L72">
         <v>5</v>
@@ -6886,14 +6888,14 @@
       <c r="H73">
         <v>2093.5825920000002</v>
       </c>
-      <c r="I73">
-        <v>5.7966949491194991E-2</v>
+      <c r="I73" s="4">
+        <v>5.8104930131935552E-2</v>
       </c>
       <c r="J73">
         <v>4062.9678629999999</v>
       </c>
-      <c r="K73">
-        <v>4.3109610567846082E-2</v>
+      <c r="K73" s="4">
+        <v>4.3241692263738599E-2</v>
       </c>
       <c r="L73">
         <v>5</v>
@@ -6927,13 +6929,13 @@
       <c r="H74">
         <v>2083.6616180000001</v>
       </c>
-      <c r="I74">
+      <c r="I74" s="4">
         <v>5.6511881767550988E-2</v>
       </c>
       <c r="J74">
         <v>4078.5600420000001</v>
       </c>
-      <c r="K74">
+      <c r="K74" s="4">
         <v>4.1145348670093222E-2</v>
       </c>
       <c r="L74">
@@ -6968,14 +6970,14 @@
       <c r="H75">
         <v>2122.0239470000001</v>
       </c>
-      <c r="I75">
-        <v>5.4994350781457188E-2</v>
+      <c r="I75" s="4">
+        <v>5.5296505340422852E-2</v>
       </c>
       <c r="J75">
         <v>4146.5667830000002</v>
       </c>
-      <c r="K75">
-        <v>4.0463542942990233E-2</v>
+      <c r="K75" s="4">
+        <v>4.065277617464802E-2</v>
       </c>
       <c r="L75">
         <v>5.25</v>
@@ -7009,14 +7011,14 @@
       <c r="H76">
         <v>2167.6918799999999</v>
       </c>
-      <c r="I76">
-        <v>5.7532745224104558E-2</v>
+      <c r="I76" s="4">
+        <v>5.821082015657561E-2</v>
       </c>
       <c r="J76">
         <v>4245.6531349999996</v>
       </c>
-      <c r="K76">
-        <v>4.3602889657118997E-2</v>
+      <c r="K76" s="4">
+        <v>4.424031547380352E-2</v>
       </c>
       <c r="L76">
         <v>5.25</v>
@@ -7050,14 +7052,14 @@
       <c r="H77">
         <v>2269.7607360000002</v>
       </c>
-      <c r="I77">
-        <v>5.3787408820656427E-2</v>
+      <c r="I77" s="4">
+        <v>5.4403075627489958E-2</v>
       </c>
       <c r="J77">
         <v>4399.9824550000003</v>
       </c>
-      <c r="K77">
-        <v>4.115649768495519E-2</v>
+      <c r="K77" s="4">
+        <v>4.1744177375047799E-2</v>
       </c>
       <c r="L77">
         <v>5.5</v>
@@ -7091,14 +7093,14 @@
       <c r="H78">
         <v>2330.57141</v>
       </c>
-      <c r="I78">
-        <v>5.3257642351992242E-2</v>
+      <c r="I78" s="4">
+        <v>5.3756776937013841E-2</v>
       </c>
       <c r="J78">
         <v>4526.5504179999998</v>
       </c>
-      <c r="K78">
-        <v>4.1157268559677877E-2</v>
+      <c r="K78" s="4">
+        <v>4.1691159316374952E-2</v>
       </c>
       <c r="L78">
         <v>5.5</v>
@@ -7132,14 +7134,14 @@
       <c r="H79">
         <v>2394.7625899999998</v>
       </c>
-      <c r="I79">
-        <v>5.2509306136998661E-2</v>
+      <c r="I79" s="4">
+        <v>5.292654290858801E-2</v>
       </c>
       <c r="J79">
         <v>4676.6022149999999</v>
       </c>
-      <c r="K79">
-        <v>4.109303025406158E-2</v>
+      <c r="K79" s="4">
+        <v>4.1589395768211329E-2</v>
       </c>
       <c r="L79">
         <v>5.75</v>
@@ -7173,14 +7175,14 @@
       <c r="H80">
         <v>2440.077123</v>
       </c>
-      <c r="I80">
-        <v>5.2687560830080679E-2</v>
+      <c r="I80" s="4">
+        <v>5.2876682243526603E-2</v>
       </c>
       <c r="J80">
         <v>4766.5243909999999</v>
       </c>
-      <c r="K80">
-        <v>4.0742638082415218E-2</v>
+      <c r="K80" s="4">
+        <v>4.1099754166321133E-2</v>
       </c>
       <c r="L80">
         <v>6</v>
@@ -7214,14 +7216,14 @@
       <c r="H81">
         <v>2529.017875</v>
       </c>
-      <c r="I81">
-        <v>5.0901350108902073E-2</v>
+      <c r="I81" s="4">
+        <v>5.0853247108237368E-2</v>
       </c>
       <c r="J81">
         <v>4969.8603109999985</v>
       </c>
-      <c r="K81">
-        <v>3.9329544077826649E-2</v>
+      <c r="K81" s="4">
+        <v>3.9479854503953631E-2</v>
       </c>
       <c r="L81">
         <v>6.25</v>
@@ -7255,14 +7257,14 @@
       <c r="H82">
         <v>2601.3375289999999</v>
       </c>
-      <c r="I82">
-        <v>5.0662389307184537E-2</v>
+      <c r="I82" s="4">
+        <v>5.0589086746358869E-2</v>
       </c>
       <c r="J82">
         <v>5125.7189829999998</v>
       </c>
-      <c r="K82">
-        <v>3.9765678169548298E-2</v>
+      <c r="K82" s="4">
+        <v>3.9934570308457082E-2</v>
       </c>
       <c r="L82">
         <v>6.5</v>
@@ -7296,14 +7298,14 @@
       <c r="H83">
         <v>2711.0647589999999</v>
       </c>
-      <c r="I83">
-        <v>5.0794344930328778E-2</v>
+      <c r="I83" s="4">
+        <v>5.0653760618802078E-2</v>
       </c>
       <c r="J83">
         <v>5326.0372900000002</v>
       </c>
-      <c r="K83">
-        <v>4.0057785368183323E-2</v>
+      <c r="K83" s="4">
+        <v>4.0177665205439958E-2</v>
       </c>
       <c r="L83">
         <v>6.5</v>
@@ -7337,14 +7339,14 @@
       <c r="H84">
         <v>2832.3490539999998</v>
       </c>
-      <c r="I84">
-        <v>5.2831500133463598E-2</v>
+      <c r="I84" s="4">
+        <v>5.2916536621407523E-2</v>
       </c>
       <c r="J84">
         <v>5520.0780080000004</v>
       </c>
-      <c r="K84">
-        <v>4.1646970143665703E-2</v>
+      <c r="K84" s="4">
+        <v>4.1841384054205989E-2</v>
       </c>
       <c r="L84">
         <v>6.5</v>
@@ -7378,14 +7380,14 @@
       <c r="H85">
         <v>2896.6231290000001</v>
       </c>
-      <c r="I85">
-        <v>5.3861638038842759E-2</v>
+      <c r="I85" s="4">
+        <v>5.3999618679583319E-2</v>
       </c>
       <c r="J85">
         <v>5637.2790850000001</v>
       </c>
-      <c r="K85">
-        <v>4.3796638243606113E-2</v>
+      <c r="K85" s="4">
+        <v>4.3928719939498637E-2</v>
       </c>
       <c r="L85">
         <v>6.5</v>
@@ -7419,13 +7421,13 @@
       <c r="H86">
         <v>2926.0300379999999</v>
       </c>
-      <c r="I86">
+      <c r="I86" s="4">
         <v>5.3248700107842162E-2</v>
       </c>
       <c r="J86">
         <v>5683.296918</v>
       </c>
-      <c r="K86">
+      <c r="K86" s="4">
         <v>4.3687944441828649E-2</v>
       </c>
       <c r="L86">
@@ -7460,14 +7462,14 @@
       <c r="H87">
         <v>2999.1562669999998</v>
       </c>
-      <c r="I87">
-        <v>5.2142520292158517E-2</v>
+      <c r="I87" s="4">
+        <v>5.2444674851124182E-2</v>
       </c>
       <c r="J87">
         <v>5782.4016420000007</v>
       </c>
-      <c r="K87">
-        <v>4.3664197692388808E-2</v>
+      <c r="K87" s="4">
+        <v>4.3853430924046602E-2</v>
       </c>
       <c r="L87">
         <v>6.25</v>
@@ -7501,14 +7503,14 @@
       <c r="H88">
         <v>3046.1982990000001</v>
       </c>
-      <c r="I88">
-        <v>5.1955416907326538E-2</v>
+      <c r="I88" s="4">
+        <v>5.263349183979759E-2</v>
       </c>
       <c r="J88">
         <v>5833.4495999999999</v>
       </c>
-      <c r="K88">
-        <v>4.2756101542457708E-2</v>
+      <c r="K88" s="4">
+        <v>4.3393527359142217E-2</v>
       </c>
       <c r="L88">
         <v>6</v>
@@ -7542,14 +7544,14 @@
       <c r="H89">
         <v>3096.3306299999999</v>
       </c>
-      <c r="I89">
-        <v>5.2910412348186137E-2</v>
+      <c r="I89" s="4">
+        <v>5.3526079155019668E-2</v>
       </c>
       <c r="J89">
         <v>5899.6513850000001</v>
       </c>
-      <c r="K89">
-        <v>4.3854913785810051E-2</v>
+      <c r="K89" s="4">
+        <v>4.444259347590266E-2</v>
       </c>
       <c r="L89">
         <v>5</v>
@@ -7583,14 +7585,14 @@
       <c r="H90">
         <v>3145.531309</v>
       </c>
-      <c r="I90">
-        <v>5.374904973137732E-2</v>
+      <c r="I90" s="4">
+        <v>5.4248184316398919E-2</v>
       </c>
       <c r="J90">
         <v>5980.9730159999999</v>
       </c>
-      <c r="K90">
-        <v>4.432534317042016E-2</v>
+      <c r="K90" s="4">
+        <v>4.4859233927117222E-2</v>
       </c>
       <c r="L90">
         <v>4</v>
@@ -7624,14 +7626,14 @@
       <c r="H91">
         <v>3179.6023049999999</v>
       </c>
-      <c r="I91">
-        <v>5.674521096341429E-2</v>
+      <c r="I91" s="4">
+        <v>5.7162447735003639E-2</v>
       </c>
       <c r="J91">
         <v>6046.0968300000004</v>
       </c>
-      <c r="K91">
-        <v>4.734890398759671E-2</v>
+      <c r="K91" s="4">
+        <v>4.784526950174646E-2</v>
       </c>
       <c r="L91">
         <v>3</v>
@@ -7665,14 +7667,14 @@
       <c r="H92">
         <v>3225.8115579999999</v>
       </c>
-      <c r="I92">
-        <v>5.8152847294064267E-2</v>
+      <c r="I92" s="4">
+        <v>5.8341968707510183E-2</v>
       </c>
       <c r="J92">
         <v>6136.1400439999998</v>
       </c>
-      <c r="K92">
-        <v>4.8494214489751893E-2</v>
+      <c r="K92" s="4">
+        <v>4.88513305736578E-2</v>
       </c>
       <c r="L92">
         <v>2</v>
@@ -7706,14 +7708,14 @@
       <c r="H93">
         <v>3268.6422729999999</v>
       </c>
-      <c r="I93">
-        <v>5.9100033574170242E-2</v>
+      <c r="I93" s="4">
+        <v>5.9051930573505537E-2</v>
       </c>
       <c r="J93">
         <v>6220.39282</v>
       </c>
-      <c r="K93">
-        <v>4.87622493814696E-2</v>
+      <c r="K93" s="4">
+        <v>4.8912559807596581E-2</v>
       </c>
       <c r="L93">
         <v>1.25</v>
@@ -7747,14 +7749,14 @@
       <c r="H94">
         <v>3304.2603730000001</v>
       </c>
-      <c r="I94">
-        <v>6.062614797983449E-2</v>
+      <c r="I94" s="4">
+        <v>6.0552845419008808E-2</v>
       </c>
       <c r="J94">
         <v>6289.6108960000001</v>
       </c>
-      <c r="K94">
-        <v>4.9961124362086051E-2</v>
+      <c r="K94" s="4">
+        <v>5.0130016500994828E-2</v>
       </c>
       <c r="L94">
         <v>1.25</v>
@@ -7788,14 +7790,14 @@
       <c r="H95">
         <v>3362.6850679999998</v>
       </c>
-      <c r="I95">
-        <v>6.3170222432297848E-2</v>
+      <c r="I95" s="4">
+        <v>6.3029638120771142E-2</v>
       </c>
       <c r="J95">
         <v>6416.8525099999997</v>
       </c>
-      <c r="K95">
-        <v>5.1564448624050963E-2</v>
+      <c r="K95" s="4">
+        <v>5.1684328461307591E-2</v>
       </c>
       <c r="L95">
         <v>1.25</v>
@@ -7829,14 +7831,14 @@
       <c r="H96">
         <v>3429.6953109999999</v>
       </c>
-      <c r="I96">
-        <v>6.664310348741373E-2</v>
+      <c r="I96" s="4">
+        <v>6.6728139975357648E-2</v>
       </c>
       <c r="J96">
         <v>6535.4703410000002</v>
       </c>
-      <c r="K96">
-        <v>5.5311696778759023E-2</v>
+      <c r="K96" s="4">
+        <v>5.5506110689299309E-2</v>
       </c>
       <c r="L96">
         <v>1.25</v>
@@ -7870,14 +7872,14 @@
       <c r="H97">
         <v>3456.9778649999998</v>
       </c>
-      <c r="I97">
-        <v>6.7854577686699252E-2</v>
+      <c r="I97" s="4">
+        <v>6.7992558327439806E-2</v>
       </c>
       <c r="J97">
         <v>6610.5684780000001</v>
       </c>
-      <c r="K97">
-        <v>5.6011305206714303E-2</v>
+      <c r="K97" s="4">
+        <v>5.6143386902606833E-2</v>
       </c>
       <c r="L97">
         <v>1.25</v>
@@ -7911,13 +7913,13 @@
       <c r="H98">
         <v>3439.8295840000001</v>
       </c>
-      <c r="I98">
+      <c r="I98" s="4">
         <v>7.0189265515660501E-2</v>
       </c>
       <c r="J98">
         <v>6577.683102</v>
       </c>
-      <c r="K98">
+      <c r="K98" s="4">
         <v>5.9257019676348652E-2</v>
       </c>
       <c r="L98">
@@ -7952,14 +7954,14 @@
       <c r="H99">
         <v>3472.6644339999998</v>
       </c>
-      <c r="I99">
-        <v>7.0799436635054516E-2</v>
+      <c r="I99" s="4">
+        <v>7.1101591194020181E-2</v>
       </c>
       <c r="J99">
         <v>6649.1859160000004</v>
       </c>
-      <c r="K99">
-        <v>5.9930260601314678E-2</v>
+      <c r="K99" s="4">
+        <v>6.0119493832972458E-2</v>
       </c>
       <c r="L99">
         <v>1.25</v>
@@ -7993,14 +7995,14 @@
       <c r="H100">
         <v>3495.8816959999999</v>
       </c>
-      <c r="I100">
-        <v>6.9749445081418962E-2</v>
+      <c r="I100" s="4">
+        <v>7.0427520013890008E-2</v>
       </c>
       <c r="J100">
         <v>6725.9597240000003</v>
       </c>
-      <c r="K100">
-        <v>5.876777437924554E-2</v>
+      <c r="K100" s="4">
+        <v>5.9405200195930062E-2</v>
       </c>
       <c r="L100">
         <v>1.25</v>
@@ -8034,14 +8036,14 @@
       <c r="H101">
         <v>3535.6035999999999</v>
       </c>
-      <c r="I101">
-        <v>7.1471481750251309E-2</v>
+      <c r="I101" s="4">
+        <v>7.208714855708484E-2</v>
       </c>
       <c r="J101">
         <v>6819.8114840000007</v>
       </c>
-      <c r="K101">
-        <v>5.9592081688609952E-2</v>
+      <c r="K101" s="4">
+        <v>6.0179761378702561E-2</v>
       </c>
       <c r="L101">
         <v>1.25</v>
@@ -8075,14 +8077,14 @@
       <c r="H102">
         <v>3575.9268630000001</v>
       </c>
-      <c r="I102">
-        <v>7.2346251815449958E-2</v>
+      <c r="I102" s="4">
+        <v>7.2845386400471557E-2</v>
       </c>
       <c r="J102">
         <v>6912.3054920000004</v>
       </c>
-      <c r="K102">
-        <v>6.0024366709965811E-2</v>
+      <c r="K102" s="4">
+        <v>6.0558257466662872E-2</v>
       </c>
       <c r="L102">
         <v>1.5</v>
@@ -8116,14 +8118,14 @@
       <c r="H103">
         <v>3584.3366620000002</v>
       </c>
-      <c r="I103">
-        <v>7.4654907035614684E-2</v>
+      <c r="I103" s="4">
+        <v>7.5072143807204034E-2</v>
       </c>
       <c r="J103">
         <v>6977.7448180000001</v>
       </c>
-      <c r="K103">
-        <v>6.1631735534879002E-2</v>
+      <c r="K103" s="4">
+        <v>6.2128101049028737E-2</v>
       </c>
       <c r="L103">
         <v>1.75</v>
@@ -8157,14 +8159,14 @@
       <c r="H104">
         <v>3912.3106440000001</v>
       </c>
-      <c r="I104">
-        <v>7.4566341568943414E-2</v>
+      <c r="I104" s="4">
+        <v>7.4755462982389331E-2</v>
       </c>
       <c r="J104">
         <v>7063.5350340200002</v>
       </c>
-      <c r="K104">
-        <v>6.1818222205465082E-2</v>
+      <c r="K104" s="4">
+        <v>6.2175338289370989E-2</v>
       </c>
       <c r="L104">
         <v>2</v>
@@ -8198,14 +8200,14 @@
       <c r="H105">
         <v>4272.7485489999999</v>
       </c>
-      <c r="I105">
-        <v>7.3351270610501937E-2</v>
+      <c r="I105" s="4">
+        <v>7.3303167609837225E-2</v>
       </c>
       <c r="J105">
         <v>7200.5011758100009</v>
       </c>
-      <c r="K105">
-        <v>6.1571566386233158E-2</v>
+      <c r="K105" s="4">
+        <v>6.1721876812360139E-2</v>
       </c>
       <c r="L105">
         <v>2.5</v>
@@ -8239,14 +8241,14 @@
       <c r="H106">
         <v>4662.773099</v>
       </c>
-      <c r="I106">
-        <v>7.0779903855549803E-2</v>
+      <c r="I106" s="4">
+        <v>7.0706601294724128E-2</v>
       </c>
       <c r="J106">
         <v>7361.6614523999997</v>
       </c>
-      <c r="K106">
-        <v>5.9958698188727788E-2</v>
+      <c r="K106" s="4">
+        <v>6.0127590327636572E-2</v>
       </c>
       <c r="L106">
         <v>3</v>
@@ -8280,14 +8282,14 @@
       <c r="H107">
         <v>5094.0788284</v>
       </c>
-      <c r="I107">
-        <v>7.0165525725680633E-2</v>
+      <c r="I107" s="4">
+        <v>7.0024941414153927E-2</v>
       </c>
       <c r="J107">
         <v>7555.5404244999991</v>
       </c>
-      <c r="K107">
-        <v>5.9936106830800417E-2</v>
+      <c r="K107" s="4">
+        <v>6.005598666805706E-2</v>
       </c>
       <c r="L107">
         <v>3</v>
@@ -8321,14 +8323,14 @@
       <c r="H108">
         <v>5236.3632733799996</v>
       </c>
-      <c r="I108">
-        <v>6.8067711598639391E-2</v>
+      <c r="I108" s="4">
+        <v>6.8152748086583309E-2</v>
       </c>
       <c r="J108">
         <v>7759.8427391699997</v>
       </c>
-      <c r="K108">
-        <v>5.8615900680145591E-2</v>
+      <c r="K108" s="4">
+        <v>5.8810314590685878E-2</v>
       </c>
       <c r="L108">
         <v>3</v>
@@ -8362,14 +8364,14 @@
       <c r="H109">
         <v>5303.6694754800001</v>
       </c>
-      <c r="I109">
-        <v>6.8307685699038043E-2</v>
+      <c r="I109" s="4">
+        <v>6.8445666339778596E-2</v>
       </c>
       <c r="J109">
         <v>7884.1293225199997</v>
       </c>
-      <c r="K109">
-        <v>5.8280310354830972E-2</v>
+      <c r="K109" s="4">
+        <v>5.8412392050723502E-2</v>
       </c>
       <c r="L109">
         <v>3</v>
@@ -8403,13 +8405,13 @@
       <c r="H110">
         <v>5271.8222215699998</v>
       </c>
-      <c r="I110">
+      <c r="I110" s="4">
         <v>6.6987865020385506E-2</v>
       </c>
       <c r="J110">
         <v>7864.5071498400002</v>
       </c>
-      <c r="K110">
+      <c r="K110" s="4">
         <v>5.6794435599068292E-2</v>
       </c>
       <c r="L110">
@@ -8444,14 +8446,14 @@
       <c r="H111">
         <v>5368.7569914599999</v>
       </c>
-      <c r="I111">
-        <v>6.5276745033706993E-2</v>
+      <c r="I111" s="4">
+        <v>6.5578899592672657E-2</v>
       </c>
       <c r="J111">
         <v>8007.8663106399999</v>
       </c>
-      <c r="K111">
-        <v>5.5525343390765813E-2</v>
+      <c r="K111" s="4">
+        <v>5.5714576622423587E-2</v>
       </c>
       <c r="L111">
         <v>3.5</v>
@@ -8485,14 +8487,14 @@
       <c r="H112">
         <v>5477.4377836900003</v>
       </c>
-      <c r="I112">
-        <v>6.1866473987705617E-2</v>
+      <c r="I112" s="4">
+        <v>6.2544548920176662E-2</v>
       </c>
       <c r="J112">
         <v>8179.8068875700001</v>
       </c>
-      <c r="K112">
-        <v>5.220357785208031E-2</v>
+      <c r="K112" s="4">
+        <v>5.2841003668764833E-2</v>
       </c>
       <c r="L112">
         <v>3.75</v>
@@ -8526,14 +8528,14 @@
       <c r="H113">
         <v>5551.0687348299998</v>
       </c>
-      <c r="I113">
-        <v>6.2430657423384717E-2</v>
+      <c r="I113" s="4">
+        <v>6.3046324230218248E-2</v>
       </c>
       <c r="J113">
         <v>8284.2491023999992</v>
       </c>
-      <c r="K113">
-        <v>5.2433244629997662E-2</v>
+      <c r="K113" s="4">
+        <v>5.3020924320090257E-2</v>
       </c>
       <c r="L113">
         <v>4</v>
@@ -8567,14 +8569,14 @@
       <c r="H114">
         <v>5633.5485502800002</v>
       </c>
-      <c r="I114">
-        <v>6.3256836959660542E-2</v>
+      <c r="I114" s="4">
+        <v>6.3755971544682141E-2</v>
       </c>
       <c r="J114">
         <v>8398.7586886900008</v>
       </c>
-      <c r="K114">
-        <v>5.2755879661456388E-2</v>
+      <c r="K114" s="4">
+        <v>5.328977041815345E-2</v>
       </c>
       <c r="L114">
         <v>4.25</v>
@@ -8608,14 +8610,14 @@
       <c r="H115">
         <v>5662.8610547999997</v>
       </c>
-      <c r="I115">
-        <v>6.2503256104319005E-2</v>
+      <c r="I115" s="4">
+        <v>6.2920492875908354E-2</v>
       </c>
       <c r="J115">
         <v>8462.9789149700009</v>
       </c>
-      <c r="K115">
-        <v>5.2325460742371259E-2</v>
+      <c r="K115" s="4">
+        <v>5.2821826256521008E-2</v>
       </c>
       <c r="L115">
         <v>4.25</v>
@@ -8649,14 +8651,14 @@
       <c r="H116">
         <v>5725.6008683399996</v>
       </c>
-      <c r="I116">
-        <v>6.484179433679077E-2</v>
+      <c r="I116" s="4">
+        <v>6.5030915750236687E-2</v>
       </c>
       <c r="J116">
         <v>8553.0507401600007</v>
       </c>
-      <c r="K116">
-        <v>5.3915973243096542E-2</v>
+      <c r="K116" s="4">
+        <v>5.4273089327002449E-2</v>
       </c>
       <c r="L116">
         <v>4.25</v>
@@ -8690,14 +8692,14 @@
       <c r="H117">
         <v>5812.0590015899998</v>
       </c>
-      <c r="I117">
-        <v>6.4897786107131192E-2</v>
+      <c r="I117" s="4">
+        <v>6.484968310646648E-2</v>
       </c>
       <c r="J117">
         <v>8679.5502381700007</v>
       </c>
-      <c r="K117">
-        <v>5.3909079515007112E-2</v>
+      <c r="K117" s="4">
+        <v>5.4059389941134087E-2</v>
       </c>
       <c r="L117">
         <v>4.25</v>
@@ -8731,14 +8733,14 @@
       <c r="H118">
         <v>5921.3550723699991</v>
       </c>
-      <c r="I118">
-        <v>6.3573078307402636E-2</v>
+      <c r="I118" s="4">
+        <v>6.3499775746576961E-2</v>
       </c>
       <c r="J118">
         <v>8868.6136846999998</v>
       </c>
-      <c r="K118">
-        <v>5.2633213856133267E-2</v>
+      <c r="K118" s="4">
+        <v>5.2802105995042037E-2</v>
       </c>
       <c r="L118">
         <v>4.25</v>
@@ -8772,14 +8774,14 @@
       <c r="H119">
         <v>6041.26420745</v>
       </c>
-      <c r="I119">
-        <v>6.4512318207579855E-2</v>
+      <c r="I119" s="4">
+        <v>6.4371733896053149E-2</v>
       </c>
       <c r="J119">
         <v>9033.4428496799992</v>
       </c>
-      <c r="K119">
-        <v>5.3489718240364373E-2</v>
+      <c r="K119" s="4">
+        <v>5.3609598077621001E-2</v>
       </c>
       <c r="L119">
         <v>4.25</v>
@@ -8813,14 +8815,14 @@
       <c r="H120">
         <v>6175.7699421699999</v>
       </c>
-      <c r="I120">
-        <v>6.413490617156041E-2</v>
+      <c r="I120" s="4">
+        <v>6.4219942659504328E-2</v>
       </c>
       <c r="J120">
         <v>9235.2566162600015</v>
       </c>
-      <c r="K120">
-        <v>5.3104082655496383E-2</v>
+      <c r="K120" s="4">
+        <v>5.329849656603667E-2</v>
       </c>
       <c r="L120">
         <v>4.25</v>
@@ -8854,14 +8856,14 @@
       <c r="H121">
         <v>6246.67535013</v>
       </c>
-      <c r="I121">
-        <v>6.5634165810826081E-2</v>
+      <c r="I121" s="4">
+        <v>6.5772146451566635E-2</v>
       </c>
       <c r="J121">
         <v>9357.5380726099993</v>
       </c>
-      <c r="K121">
-        <v>5.4190324227902542E-2</v>
+      <c r="K121" s="4">
+        <v>5.4322405923795072E-2</v>
       </c>
       <c r="L121">
         <v>4.25</v>
@@ -8895,13 +8897,13 @@
       <c r="H122">
         <v>6186.8370042799997</v>
       </c>
-      <c r="I122">
+      <c r="I122" s="4">
         <v>6.5700450546669009E-2</v>
       </c>
       <c r="J122">
         <v>9302.1009763799993</v>
       </c>
-      <c r="K122">
+      <c r="K122" s="4">
         <v>5.3823195814720122E-2</v>
       </c>
       <c r="L122">
@@ -8936,14 +8938,14 @@
       <c r="H123">
         <v>6242.1498302399996</v>
       </c>
-      <c r="I123">
-        <v>6.4930003196697963E-2</v>
+      <c r="I123" s="4">
+        <v>6.5232157755663628E-2</v>
       </c>
       <c r="J123">
         <v>9397.9161654300005</v>
       </c>
-      <c r="K123">
-        <v>5.3236716165823338E-2</v>
+      <c r="K123" s="4">
+        <v>5.3425949397481132E-2</v>
       </c>
       <c r="L123">
         <v>4.25</v>
@@ -8977,14 +8979,14 @@
       <c r="H124">
         <v>6315.9264734600001</v>
       </c>
-      <c r="I124">
-        <v>6.4455621810869307E-2</v>
+      <c r="I124" s="4">
+        <v>6.5133696743340352E-2</v>
       </c>
       <c r="J124">
         <v>9508.0005661399991</v>
       </c>
-      <c r="K124">
-        <v>5.2888069915997288E-2</v>
+      <c r="K124" s="4">
+        <v>5.3525495732681803E-2</v>
       </c>
       <c r="L124">
         <v>4.25</v>
@@ -9018,14 +9020,14 @@
       <c r="H125">
         <v>6380.6189163999998</v>
       </c>
-      <c r="I125">
-        <v>6.6714895585464909E-2</v>
+      <c r="I125" s="4">
+        <v>6.733056239229844E-2</v>
       </c>
       <c r="J125">
         <v>9599.1133784600006</v>
       </c>
-      <c r="K125">
-        <v>5.4932022653497073E-2</v>
+      <c r="K125" s="4">
+        <v>5.5519702343589682E-2</v>
       </c>
       <c r="L125">
         <v>4.25</v>
@@ -9059,14 +9061,14 @@
       <c r="H126">
         <v>6492.0052267400006</v>
       </c>
-      <c r="I126">
-        <v>6.6523495188175366E-2</v>
+      <c r="I126" s="4">
+        <v>6.7022629773196965E-2</v>
       </c>
       <c r="J126">
         <v>9766.9052314199998</v>
       </c>
-      <c r="K126">
-        <v>5.4598088243827239E-2</v>
+      <c r="K126" s="4">
+        <v>5.51319790005243E-2</v>
       </c>
       <c r="L126">
         <v>4.25</v>
@@ -9100,14 +9102,14 @@
       <c r="H127">
         <v>6524.0266904499986</v>
       </c>
-      <c r="I127">
-        <v>6.7711290485792816E-2</v>
+      <c r="I127" s="4">
+        <v>6.8128527257382165E-2</v>
       </c>
       <c r="J127">
         <v>9816.3173731200004</v>
       </c>
-      <c r="K127">
-        <v>5.5571754570369267E-2</v>
+      <c r="K127" s="4">
+        <v>5.6068120084519023E-2</v>
       </c>
       <c r="L127">
         <v>4.25</v>
@@ -9141,14 +9143,14 @@
       <c r="H128">
         <v>6601.0925136100004</v>
       </c>
-      <c r="I128">
-        <v>6.822045091599549E-2</v>
+      <c r="I128" s="4">
+        <v>6.8409572329441407E-2</v>
       </c>
       <c r="J128">
         <v>9922.1421894800005</v>
       </c>
-      <c r="K128">
-        <v>5.5707584094315157E-2</v>
+      <c r="K128" s="4">
+        <v>5.6064700178221058E-2</v>
       </c>
       <c r="L128">
         <v>4.25</v>
@@ -9182,14 +9184,14 @@
       <c r="H129">
         <v>6674.5198953299996</v>
       </c>
-      <c r="I129">
-        <v>7.0697600813774089E-2</v>
+      <c r="I129" s="4">
+        <v>7.0649497813109377E-2</v>
       </c>
       <c r="J129">
         <v>10046.7969486</v>
       </c>
-      <c r="K129">
-        <v>5.7269894712692927E-2</v>
+      <c r="K129" s="4">
+        <v>5.7420205138819909E-2</v>
       </c>
       <c r="L129">
         <v>4.25</v>
@@ -9223,14 +9225,14 @@
       <c r="H130">
         <v>6763.7167086999998</v>
       </c>
-      <c r="I130">
-        <v>7.0992818341366143E-2</v>
+      <c r="I130" s="4">
+        <v>7.0919515780540468E-2</v>
       </c>
       <c r="J130">
         <v>10186.77912967</v>
       </c>
-      <c r="K130">
-        <v>5.7894740632852222E-2</v>
+      <c r="K130" s="4">
+        <v>5.8063632771760992E-2</v>
       </c>
       <c r="L130">
         <v>4.25</v>
@@ -9264,14 +9266,14 @@
       <c r="H131">
         <v>6884.1508504399999</v>
       </c>
-      <c r="I131">
-        <v>7.1724290456124024E-2</v>
+      <c r="I131" s="4">
+        <v>7.1583706144597317E-2</v>
       </c>
       <c r="J131">
         <v>10356.158876900001</v>
       </c>
-      <c r="K131">
-        <v>5.8453154569433133E-2</v>
+      <c r="K131" s="4">
+        <v>5.8573034406689761E-2</v>
       </c>
       <c r="L131">
         <v>4.25</v>
@@ -9305,14 +9307,14 @@
       <c r="H132">
         <v>7036.4793989500004</v>
       </c>
-      <c r="I132">
-        <v>7.3039501492157419E-2</v>
+      <c r="I132" s="4">
+        <v>7.3124537980101337E-2</v>
       </c>
       <c r="J132">
         <v>10574.68853976</v>
       </c>
-      <c r="K132">
-        <v>5.9457772961243362E-2</v>
+      <c r="K132" s="4">
+        <v>5.9652186871783662E-2</v>
       </c>
       <c r="L132">
         <v>4.25</v>
@@ -9346,14 +9348,14 @@
       <c r="H133">
         <v>7017.5664852399996</v>
       </c>
-      <c r="I133">
-        <v>6.8438292429729847E-2</v>
+      <c r="I133" s="4">
+        <v>6.8576273070470414E-2</v>
       </c>
       <c r="J133">
         <v>10578.21333837</v>
       </c>
-      <c r="K133">
-        <v>5.6137960115516132E-2</v>
+      <c r="K133" s="4">
+        <v>5.6270041811408662E-2</v>
       </c>
       <c r="L133">
         <v>4.25</v>
@@ -9387,13 +9389,13 @@
       <c r="H134">
         <v>6994.9729479199996</v>
       </c>
-      <c r="I134">
+      <c r="I134" s="4">
         <v>6.8381096850736595E-2</v>
       </c>
       <c r="J134">
         <v>10593.22620137</v>
       </c>
-      <c r="K134">
+      <c r="K134" s="4">
         <v>5.5114065991009771E-2</v>
       </c>
       <c r="L134">
@@ -9428,14 +9430,14 @@
       <c r="H135">
         <v>7017.3563617300006</v>
       </c>
-      <c r="I135">
-        <v>7.0940491223527941E-2</v>
+      <c r="I135" s="4">
+        <v>7.1242645782493605E-2</v>
       </c>
       <c r="J135">
         <v>10694.63997801</v>
       </c>
-      <c r="K135">
-        <v>5.7039084805285897E-2</v>
+      <c r="K135" s="4">
+        <v>5.7228318036943678E-2</v>
       </c>
       <c r="L135">
         <v>4.25</v>
@@ -9469,14 +9471,14 @@
       <c r="H136">
         <v>7056.9153317700002</v>
       </c>
-      <c r="I136">
-        <v>7.1422400525990706E-2</v>
+      <c r="I136" s="4">
+        <v>7.2100475458461752E-2</v>
       </c>
       <c r="J136">
         <v>10732.69467635</v>
       </c>
-      <c r="K136">
-        <v>5.7679583929774167E-2</v>
+      <c r="K136" s="4">
+        <v>5.831700974645869E-2</v>
       </c>
       <c r="L136">
         <v>4.25</v>
@@ -9510,14 +9512,14 @@
       <c r="H137">
         <v>7168.7382187100002</v>
       </c>
-      <c r="I137">
-        <v>7.2579810910891177E-2</v>
+      <c r="I137" s="4">
+        <v>7.3195477717724708E-2</v>
       </c>
       <c r="J137">
         <v>10899.965093860001</v>
       </c>
-      <c r="K137">
-        <v>5.7444899862894333E-2</v>
+      <c r="K137" s="4">
+        <v>5.8032579552986928E-2</v>
       </c>
       <c r="L137">
         <v>4.25</v>
@@ -9551,14 +9553,14 @@
       <c r="H138">
         <v>7271.0032377099997</v>
       </c>
-      <c r="I138">
-        <v>7.3566716628477927E-2</v>
+      <c r="I138" s="4">
+        <v>7.4065851213499526E-2</v>
       </c>
       <c r="J138">
         <v>11083.7092426</v>
       </c>
-      <c r="K138">
-        <v>5.8079470879400158E-2</v>
+      <c r="K138" s="4">
+        <v>5.8613361636097219E-2</v>
       </c>
       <c r="L138">
         <v>4.25</v>
@@ -9592,14 +9594,14 @@
       <c r="H139">
         <v>7316.0300982299996</v>
       </c>
-      <c r="I139">
-        <v>7.1801145386795398E-2</v>
+      <c r="I139" s="4">
+        <v>7.2218382158384747E-2</v>
       </c>
       <c r="J139">
         <v>11194.17080588</v>
       </c>
-      <c r="K139">
-        <v>5.6720017324836697E-2</v>
+      <c r="K139" s="4">
+        <v>5.7216382838986453E-2</v>
       </c>
       <c r="L139">
         <v>4.25</v>
@@ -9633,14 +9635,14 @@
       <c r="H140">
         <v>7345.4553875900001</v>
       </c>
-      <c r="I140">
-        <v>7.5298059193049077E-2</v>
+      <c r="I140" s="4">
+        <v>7.5487180606494994E-2</v>
       </c>
       <c r="J140">
         <v>11242.5719955</v>
       </c>
-      <c r="K140">
-        <v>5.9494104803959072E-2</v>
+      <c r="K140" s="4">
+        <v>5.9851220887864973E-2</v>
       </c>
       <c r="L140">
         <v>4.25</v>
@@ -9674,14 +9676,14 @@
       <c r="H141">
         <v>7399.3781635300002</v>
       </c>
-      <c r="I141">
-        <v>7.9211455016736876E-2</v>
+      <c r="I141" s="4">
+        <v>7.9163352016072164E-2</v>
       </c>
       <c r="J141">
         <v>11356.820464349999</v>
       </c>
-      <c r="K141">
-        <v>6.2174142188935071E-2</v>
+      <c r="K141" s="4">
+        <v>6.2324452615062052E-2</v>
       </c>
       <c r="L141">
         <v>4.25</v>
@@ -9715,14 +9717,14 @@
       <c r="H142">
         <v>7443.9502804599997</v>
       </c>
-      <c r="I142">
-        <v>8.0697075974390353E-2</v>
+      <c r="I142" s="4">
+        <v>8.0623773413564678E-2</v>
       </c>
       <c r="J142">
         <v>11449.76199483</v>
       </c>
-      <c r="K142">
-        <v>6.3123205517320133E-2</v>
+      <c r="K142" s="4">
+        <v>6.329209765622891E-2</v>
       </c>
       <c r="L142">
         <v>4.25</v>
@@ -9756,14 +9758,14 @@
       <c r="H143">
         <v>7549.2751983099997</v>
       </c>
-      <c r="I143">
-        <v>8.0587292928431808E-2</v>
+      <c r="I143" s="4">
+        <v>8.0446708616905102E-2</v>
       </c>
       <c r="J143">
         <v>11602.08688642</v>
       </c>
-      <c r="K143">
-        <v>6.3322019509797142E-2</v>
+      <c r="K143" s="4">
+        <v>6.3441899347053785E-2</v>
       </c>
       <c r="L143">
         <v>4.25</v>
@@ -9797,14 +9799,14 @@
       <c r="H144">
         <v>7646.1612642199998</v>
       </c>
-      <c r="I144">
-        <v>7.5696606592038987E-2</v>
+      <c r="I144" s="4">
+        <v>7.5781643079982905E-2</v>
       </c>
       <c r="J144">
         <v>11778.91175277</v>
       </c>
-      <c r="K144">
-        <v>5.9121793443709811E-2</v>
+      <c r="K144" s="4">
+        <v>5.9316207354250097E-2</v>
       </c>
       <c r="L144">
         <v>4</v>
@@ -9838,14 +9840,14 @@
       <c r="H145">
         <v>7704.6469238600002</v>
       </c>
-      <c r="I145">
-        <v>7.7627761061247594E-2</v>
+      <c r="I145" s="4">
+        <v>7.7765741701988148E-2</v>
       </c>
       <c r="J145">
         <v>11900.02950861</v>
       </c>
-      <c r="K145">
-        <v>6.0808208889898033E-2</v>
+      <c r="K145" s="4">
+        <v>6.0940290585790563E-2</v>
       </c>
       <c r="L145">
         <v>4</v>
@@ -9879,13 +9881,13 @@
       <c r="H146">
         <v>7646.4728383000001</v>
       </c>
-      <c r="I146">
+      <c r="I146" s="4">
         <v>7.8462253183571876E-2</v>
       </c>
       <c r="J146">
         <v>11855.89213495</v>
       </c>
-      <c r="K146">
+      <c r="K146" s="4">
         <v>6.1316236449806889E-2</v>
       </c>
       <c r="L146">
@@ -9920,14 +9922,14 @@
       <c r="H147">
         <v>7705.5992425499999</v>
       </c>
-      <c r="I147">
-        <v>7.9276840604140586E-2</v>
+      <c r="I147" s="4">
+        <v>7.957899516310625E-2</v>
       </c>
       <c r="J147">
         <v>11960.91661169</v>
       </c>
-      <c r="K147">
-        <v>6.1990644622570368E-2</v>
+      <c r="K147" s="4">
+        <v>6.2179877854228148E-2</v>
       </c>
       <c r="L147">
         <v>4</v>
@@ -9961,14 +9963,14 @@
       <c r="H148">
         <v>7760.0555636899999</v>
       </c>
-      <c r="I148">
-        <v>7.9642477699683301E-2</v>
+      <c r="I148" s="4">
+        <v>8.0320552632154346E-2</v>
       </c>
       <c r="J148">
         <v>12064.83212861</v>
       </c>
-      <c r="K148">
-        <v>6.2531909782934214E-2</v>
+      <c r="K148" s="4">
+        <v>6.3169335599618737E-2</v>
       </c>
       <c r="L148">
         <v>4</v>
@@ -10002,14 +10004,14 @@
       <c r="H149">
         <v>7808.2643688199996</v>
       </c>
-      <c r="I149">
-        <v>8.1747430365035179E-2</v>
+      <c r="I149" s="4">
+        <v>8.236309717186871E-2</v>
       </c>
       <c r="J149">
         <v>12155.796386980001</v>
       </c>
-      <c r="K149">
-        <v>6.4102269869397641E-2</v>
+      <c r="K149" s="4">
+        <v>6.4689949559490256E-2</v>
       </c>
       <c r="L149">
         <v>4</v>
@@ -10043,14 +10045,14 @@
       <c r="H150">
         <v>7812.9467608800014</v>
       </c>
-      <c r="I150">
-        <v>8.4546668626386712E-2</v>
+      <c r="I150" s="4">
+        <v>8.5045803211408311E-2</v>
       </c>
       <c r="J150">
         <v>12192.01394854</v>
       </c>
-      <c r="K150">
-        <v>6.6250789823094805E-2</v>
+      <c r="K150" s="4">
+        <v>6.6784680579791866E-2</v>
       </c>
       <c r="L150">
         <v>4</v>
@@ -10084,14 +10086,14 @@
       <c r="H151">
         <v>7825.7836045800004</v>
       </c>
-      <c r="I151">
-        <v>8.2499352069160647E-2</v>
+      <c r="I151" s="4">
+        <v>8.2916588840749997E-2</v>
       </c>
       <c r="J151">
         <v>12244.055331310001</v>
       </c>
-      <c r="K151">
-        <v>6.4997514851737201E-2</v>
+      <c r="K151" s="4">
+        <v>6.549388036588695E-2</v>
       </c>
       <c r="L151">
         <v>4</v>
@@ -10125,14 +10127,14 @@
       <c r="H152">
         <v>7867.5535649099993</v>
       </c>
-      <c r="I152">
-        <v>8.466981657146383E-2</v>
+      <c r="I152" s="4">
+        <v>8.4858937984909746E-2</v>
       </c>
       <c r="J152">
         <v>12298.53065982</v>
       </c>
-      <c r="K152">
-        <v>6.6169382061404686E-2</v>
+      <c r="K152" s="4">
+        <v>6.65264981453106E-2</v>
       </c>
       <c r="L152">
         <v>3.75</v>
@@ -10166,14 +10168,14 @@
       <c r="H153">
         <v>7935.7251720700006</v>
       </c>
-      <c r="I153">
-        <v>8.6249518076755655E-2</v>
+      <c r="I153" s="4">
+        <v>8.6201415076090943E-2</v>
       </c>
       <c r="J153">
         <v>12423.142105340001</v>
       </c>
-      <c r="K153">
-        <v>6.7115126663714136E-2</v>
+      <c r="K153" s="4">
+        <v>6.7265437089841118E-2</v>
       </c>
       <c r="L153">
         <v>3.75</v>
@@ -10207,14 +10209,14 @@
       <c r="H154">
         <v>7966.5615898699998</v>
       </c>
-      <c r="I154">
-        <v>8.5003968004465413E-2</v>
+      <c r="I154" s="4">
+        <v>8.4930665443639738E-2</v>
       </c>
       <c r="J154">
         <v>12500.12962673</v>
       </c>
-      <c r="K154">
-        <v>6.6429917877660949E-2</v>
+      <c r="K154" s="4">
+        <v>6.6598810016569726E-2</v>
       </c>
       <c r="L154">
         <v>3.5</v>
@@ -10248,14 +10250,14 @@
       <c r="H155">
         <v>8042.4083267100004</v>
       </c>
-      <c r="I155">
-        <v>8.475904770035679E-2</v>
+      <c r="I155" s="4">
+        <v>8.4618463388830084E-2</v>
       </c>
       <c r="J155">
         <v>12636.29765122</v>
       </c>
-      <c r="K155">
-        <v>6.5533049496685147E-2</v>
+      <c r="K155" s="4">
+        <v>6.565292933394179E-2</v>
       </c>
       <c r="L155">
         <v>3.5</v>
@@ -10289,14 +10291,14 @@
       <c r="H156">
         <v>8160.5943862800004</v>
       </c>
-      <c r="I156">
-        <v>8.6271227295642183E-2</v>
+      <c r="I156" s="4">
+        <v>8.6356263783586101E-2</v>
       </c>
       <c r="J156">
         <v>12818.26374996</v>
       </c>
-      <c r="K156">
-        <v>6.6765140607735529E-2</v>
+      <c r="K156" s="4">
+        <v>6.6959554518275816E-2</v>
       </c>
       <c r="L156">
         <v>3.5</v>
@@ -10330,14 +10332,14 @@
       <c r="H157">
         <v>8153.8438916599998</v>
       </c>
-      <c r="I157">
-        <v>7.9559487344830232E-2</v>
+      <c r="I157" s="4">
+        <v>7.9697467985570786E-2</v>
       </c>
       <c r="J157">
         <v>12920.909428679999</v>
       </c>
-      <c r="K157">
-        <v>6.1798644195490068E-2</v>
+      <c r="K157" s="4">
+        <v>6.1930725891382592E-2</v>
       </c>
       <c r="L157">
         <v>3.5</v>
@@ -10371,13 +10373,13 @@
       <c r="H158">
         <v>8095.5793834699998</v>
       </c>
-      <c r="I158">
+      <c r="I158" s="4">
         <v>7.8282619259346861E-2</v>
       </c>
       <c r="J158">
         <v>12930.470019939999</v>
       </c>
-      <c r="K158">
+      <c r="K158" s="4">
         <v>6.1082719932222918E-2</v>
       </c>
       <c r="L158">
@@ -10412,14 +10414,14 @@
       <c r="H159">
         <v>8165.5200198800003</v>
       </c>
-      <c r="I159">
-        <v>7.6405039976120429E-2</v>
+      <c r="I159" s="4">
+        <v>7.6707194535086093E-2</v>
       </c>
       <c r="J159">
         <v>13048.19116486</v>
       </c>
-      <c r="K159">
-        <v>6.0251892747671842E-2</v>
+      <c r="K159" s="4">
+        <v>6.044112597932963E-2</v>
       </c>
       <c r="L159">
         <v>3.25</v>
@@ -10453,14 +10455,14 @@
       <c r="H160">
         <v>8258.6702812399999</v>
       </c>
-      <c r="I160">
-        <v>7.6471131728694658E-2</v>
+      <c r="I160" s="4">
+        <v>7.7149206661165703E-2</v>
       </c>
       <c r="J160">
         <v>13169.101907710001</v>
       </c>
-      <c r="K160">
-        <v>6.0472446171061588E-2</v>
+      <c r="K160" s="4">
+        <v>6.1109871987746103E-2</v>
       </c>
       <c r="L160">
         <v>3.25</v>
@@ -10494,14 +10496,14 @@
       <c r="H161">
         <v>8340.3753127</v>
       </c>
-      <c r="I161">
-        <v>7.654173988605513E-2</v>
+      <c r="I161" s="4">
+        <v>7.7157406692888661E-2</v>
       </c>
       <c r="J161">
         <v>13316.859910970001</v>
       </c>
-      <c r="K161">
-        <v>6.0988828872080673E-2</v>
+      <c r="K161" s="4">
+        <v>6.1576508562173282E-2</v>
       </c>
       <c r="L161">
         <v>3.25</v>
@@ -10535,14 +10537,14 @@
       <c r="H162">
         <v>8410.5892563899997</v>
       </c>
-      <c r="I162">
-        <v>7.8958408733772828E-2</v>
+      <c r="I162" s="4">
+        <v>7.9457543318794427E-2</v>
       </c>
       <c r="J162">
         <v>13411.963453320001</v>
       </c>
-      <c r="K162">
-        <v>6.2678388790975745E-2</v>
+      <c r="K162" s="4">
+        <v>6.3212279547672806E-2</v>
       </c>
       <c r="L162">
         <v>3.25</v>
@@ -10576,14 +10578,14 @@
       <c r="H163">
         <v>8379.84422051</v>
       </c>
-      <c r="I163">
-        <v>7.730977436770553E-2</v>
+      <c r="I163" s="4">
+        <v>7.772701113929488E-2</v>
       </c>
       <c r="J163">
         <v>13405.96638387</v>
       </c>
-      <c r="K163">
-        <v>6.2289748985530947E-2</v>
+      <c r="K163" s="4">
+        <v>6.2786114499680704E-2</v>
       </c>
       <c r="L163">
         <v>3.25</v>
@@ -10617,14 +10619,14 @@
       <c r="H164">
         <v>8341.8875228500001</v>
       </c>
-      <c r="I164">
-        <v>7.3363213384291803E-2</v>
+      <c r="I164" s="4">
+        <v>7.355233479773772E-2</v>
       </c>
       <c r="J164">
         <v>13422.44654836</v>
       </c>
-      <c r="K164">
-        <v>6.0348805964899332E-2</v>
+      <c r="K164" s="4">
+        <v>6.070592204880524E-2</v>
       </c>
       <c r="L164">
         <v>3.25</v>
@@ -10658,14 +10660,14 @@
       <c r="H165">
         <v>8413.3321996600007</v>
       </c>
-      <c r="I165">
-        <v>7.5297110204339421E-2</v>
+      <c r="I165" s="4">
+        <v>7.5249007203674709E-2</v>
       </c>
       <c r="J165">
         <v>13565.90701938</v>
       </c>
-      <c r="K165">
-        <v>6.2076468687348459E-2</v>
+      <c r="K165" s="4">
+        <v>6.222677911347544E-2</v>
       </c>
       <c r="L165">
         <v>3.25</v>
@@ -10699,14 +10701,14 @@
       <c r="H166">
         <v>8488.3181081000002</v>
       </c>
-      <c r="I166">
-        <v>7.6452229710932948E-2</v>
+      <c r="I166" s="4">
+        <v>7.6378927150107273E-2</v>
       </c>
       <c r="J166">
         <v>13717.747039559999</v>
       </c>
-      <c r="K166">
-        <v>6.2758329070426638E-2</v>
+      <c r="K166" s="4">
+        <v>6.2927221209335416E-2</v>
       </c>
       <c r="L166">
         <v>3.5</v>
@@ -10740,14 +10742,14 @@
       <c r="H167">
         <v>8598.0334791599998</v>
       </c>
-      <c r="I167">
-        <v>7.7137243546420334E-2</v>
+      <c r="I167" s="4">
+        <v>7.6996659234893627E-2</v>
       </c>
       <c r="J167">
         <v>13874.0085726</v>
       </c>
-      <c r="K167">
-        <v>6.3247563711231289E-2</v>
+      <c r="K167" s="4">
+        <v>6.3367443548487931E-2</v>
       </c>
       <c r="L167">
         <v>3.5</v>
@@ -10781,14 +10783,14 @@
       <c r="H168">
         <v>8750.9560578100009</v>
       </c>
-      <c r="I168">
-        <v>7.9999361300285801E-2</v>
+      <c r="I168" s="4">
+        <v>8.0084397788229719E-2</v>
       </c>
       <c r="J168">
         <v>14103.13868077</v>
       </c>
-      <c r="K168">
-        <v>6.5136041518136761E-2</v>
+      <c r="K168" s="4">
+        <v>6.5330455428677048E-2</v>
       </c>
       <c r="L168">
         <v>3.5</v>
@@ -10822,14 +10824,14 @@
       <c r="H169">
         <v>8795.2653784100003</v>
       </c>
-      <c r="I169">
-        <v>7.6869985217647055E-2</v>
+      <c r="I169" s="4">
+        <v>7.7007965858387609E-2</v>
       </c>
       <c r="J169">
         <v>14253.83746105</v>
       </c>
-      <c r="K169">
-        <v>6.3115961295432704E-2</v>
+      <c r="K169" s="4">
+        <v>6.3248042991325221E-2</v>
       </c>
       <c r="L169">
         <v>3.75</v>
@@ -10863,13 +10865,13 @@
       <c r="H170">
         <v>8779.1838920499995</v>
       </c>
-      <c r="I170">
+      <c r="I170" s="4">
         <v>7.6395056345424164E-2</v>
       </c>
       <c r="J170">
         <v>14234.478092859999</v>
       </c>
-      <c r="K170">
+      <c r="K170" s="4">
         <v>6.3315381992970418E-2</v>
       </c>
       <c r="L170">
@@ -10904,14 +10906,14 @@
       <c r="H171">
         <v>8873.9178327999998</v>
       </c>
-      <c r="I171">
-        <v>7.5010749578853717E-2</v>
+      <c r="I171" s="4">
+        <v>7.5312904137819381E-2</v>
       </c>
       <c r="J171">
         <v>14378.06269615</v>
       </c>
-      <c r="K171">
-        <v>6.1887182183393161E-2</v>
+      <c r="K171" s="4">
+        <v>6.2076415415050948E-2</v>
       </c>
       <c r="L171">
         <v>4.25</v>
@@ -10945,14 +10947,14 @@
       <c r="H172">
         <v>8949.0686506099992</v>
       </c>
-      <c r="I172">
-        <v>7.467420477143448E-2</v>
+      <c r="I172" s="4">
+        <v>7.5352279703905525E-2</v>
       </c>
       <c r="J172">
         <v>14502.203805949999</v>
       </c>
-      <c r="K172">
-        <v>6.1862825858147362E-2</v>
+      <c r="K172" s="4">
+        <v>6.2500251674831878E-2</v>
       </c>
       <c r="L172">
         <v>4.25</v>
@@ -10986,14 +10988,14 @@
       <c r="H173">
         <v>9091.6101338799999</v>
       </c>
-      <c r="I173">
-        <v>7.4138386583736116E-2</v>
+      <c r="I173" s="4">
+        <v>7.4754053390569647E-2</v>
       </c>
       <c r="J173">
         <v>14720.70087481</v>
       </c>
-      <c r="K173">
-        <v>6.1416870459111927E-2</v>
+      <c r="K173" s="4">
+        <v>6.2004550149204543E-2</v>
       </c>
       <c r="L173">
         <v>4.25</v>
@@ -11027,14 +11029,14 @@
       <c r="H174">
         <v>9192.7787757200003</v>
       </c>
-      <c r="I174">
-        <v>7.4031378348262303E-2</v>
+      <c r="I174" s="4">
+        <v>7.4530512933283902E-2</v>
       </c>
       <c r="J174">
         <v>14876.125973509999</v>
       </c>
-      <c r="K174">
-        <v>6.3234898295277883E-2</v>
+      <c r="K174" s="4">
+        <v>6.3768789051974945E-2</v>
       </c>
       <c r="L174">
         <v>4.25</v>
@@ -11068,14 +11070,14 @@
       <c r="H175">
         <v>9241.6136557400005</v>
       </c>
-      <c r="I175">
-        <v>6.7564693916645227E-2</v>
+      <c r="I175" s="4">
+        <v>6.7981930688234576E-2</v>
       </c>
       <c r="J175">
         <v>14971.90514407</v>
       </c>
-      <c r="K175">
-        <v>5.7840977473065422E-2</v>
+      <c r="K175" s="4">
+        <v>5.8337342987215171E-2</v>
       </c>
       <c r="L175">
         <v>4.25</v>
@@ -11109,14 +11111,14 @@
       <c r="H176">
         <v>9365.434357099999</v>
       </c>
-      <c r="I176">
-        <v>6.9678273249999825E-2</v>
+      <c r="I176" s="4">
+        <v>6.9867394663445742E-2</v>
       </c>
       <c r="J176">
         <v>15149.82843989</v>
       </c>
-      <c r="K176">
-        <v>5.9504834778959938E-2</v>
+      <c r="K176" s="4">
+        <v>5.9861950862865852E-2</v>
       </c>
       <c r="L176">
         <v>4.25</v>
@@ -11150,14 +11152,14 @@
       <c r="H177">
         <v>9490.8248696200008</v>
       </c>
-      <c r="I177">
-        <v>6.8634997322640029E-2</v>
+      <c r="I177" s="4">
+        <v>6.8586894321975317E-2</v>
       </c>
       <c r="J177">
         <v>15348.41417263</v>
       </c>
-      <c r="K177">
-        <v>5.8939649990394472E-2</v>
+      <c r="K177" s="4">
+        <v>5.9089960416521453E-2</v>
       </c>
       <c r="L177">
         <v>4.25</v>
@@ -11191,14 +11193,14 @@
       <c r="H178">
         <v>9692.5291187500006</v>
       </c>
-      <c r="I178">
-        <v>6.8512550748193679E-2</v>
+      <c r="I178" s="4">
+        <v>6.8439248187368004E-2</v>
       </c>
       <c r="J178">
         <v>15637.098635099999</v>
       </c>
-      <c r="K178">
-        <v>5.87477083123134E-2</v>
+      <c r="K178" s="4">
+        <v>5.8916600451222177E-2</v>
       </c>
       <c r="L178">
         <v>4.25</v>
@@ -11232,14 +11234,14 @@
       <c r="H179">
         <v>9915.93192275</v>
       </c>
-      <c r="I179">
-        <v>6.919025922658853E-2</v>
+      <c r="I179" s="4">
+        <v>6.9049674915061823E-2</v>
       </c>
       <c r="J179">
         <v>15972.12165134</v>
       </c>
-      <c r="K179">
-        <v>5.8694530671635013E-2</v>
+      <c r="K179" s="4">
+        <v>5.8814410508891649E-2</v>
       </c>
       <c r="L179">
         <v>4.25</v>
@@ -11273,14 +11275,14 @@
       <c r="H180">
         <v>10190.416776829999</v>
       </c>
-      <c r="I180">
-        <v>7.0438466175665335E-2</v>
+      <c r="I180" s="4">
+        <v>7.0523502663609253E-2</v>
       </c>
       <c r="J180">
         <v>16358.422680449999</v>
       </c>
-      <c r="K180">
-        <v>5.9449713174121302E-2</v>
+      <c r="K180" s="4">
+        <v>5.9644127084661602E-2</v>
       </c>
       <c r="L180">
         <v>4.25</v>
@@ -11314,14 +11316,14 @@
       <c r="H181">
         <v>10387.254654480001</v>
       </c>
-      <c r="I181">
-        <v>6.8683659719160489E-2</v>
+      <c r="I181" s="4">
+        <v>6.8821640359901043E-2</v>
       </c>
       <c r="J181">
         <v>16795.659930760001</v>
       </c>
-      <c r="K181">
-        <v>5.7907138733020842E-2</v>
+      <c r="K181" s="4">
+        <v>5.8039220428913373E-2</v>
       </c>
       <c r="L181">
         <v>4.25</v>
@@ -11355,13 +11357,13 @@
       <c r="H182">
         <v>10406.403088319999</v>
       </c>
-      <c r="I182">
+      <c r="I182" s="4">
         <v>6.7060296429730298E-2</v>
       </c>
       <c r="J182">
         <v>16831.767955570002</v>
       </c>
-      <c r="K182">
+      <c r="K182" s="4">
         <v>5.6495808240709391E-2</v>
       </c>
       <c r="L182">
@@ -11396,14 +11398,14 @@
       <c r="H183">
         <v>10569.4355805</v>
       </c>
-      <c r="I183">
-        <v>6.6715816209101678E-2</v>
+      <c r="I183" s="4">
+        <v>6.7017970768067342E-2</v>
       </c>
       <c r="J183">
         <v>17083.45255469</v>
       </c>
-      <c r="K183">
-        <v>5.6946139812514618E-2</v>
+      <c r="K183" s="4">
+        <v>5.7135373044172412E-2</v>
       </c>
       <c r="L183">
         <v>4.25</v>
@@ -11437,14 +11439,14 @@
       <c r="H184">
         <v>10646.158185439999</v>
       </c>
-      <c r="I184">
-        <v>6.4840695896719966E-2</v>
+      <c r="I184" s="4">
+        <v>6.5518770829191011E-2</v>
       </c>
       <c r="J184">
         <v>17223.034069379999</v>
       </c>
-      <c r="K184">
-        <v>5.4588850758389637E-2</v>
+      <c r="K184" s="4">
+        <v>5.522627657507416E-2</v>
       </c>
       <c r="L184">
         <v>4.25</v>
@@ -11478,14 +11480,14 @@
       <c r="H185">
         <v>10760.231230859999</v>
       </c>
-      <c r="I185">
-        <v>6.5520597724745583E-2</v>
+      <c r="I185" s="4">
+        <v>6.6136264531579114E-2</v>
       </c>
       <c r="J185">
         <v>17445.65903757</v>
       </c>
-      <c r="K185">
-        <v>5.50380112645453E-2</v>
+      <c r="K185" s="4">
+        <v>5.5625690954637909E-2</v>
       </c>
       <c r="L185">
         <v>4.25</v>
@@ -11519,14 +11521,14 @@
       <c r="H186">
         <v>10908.338701979999</v>
       </c>
-      <c r="I186">
-        <v>6.4776429648184197E-2</v>
+      <c r="I186" s="4">
+        <v>6.5275564233205796E-2</v>
       </c>
       <c r="J186">
         <v>17676.777908100001</v>
       </c>
-      <c r="K186">
-        <v>5.4626809880414018E-2</v>
+      <c r="K186" s="4">
+        <v>5.5160700637111079E-2</v>
       </c>
       <c r="L186">
         <v>4</v>
@@ -11560,14 +11562,14 @@
       <c r="H187">
         <v>11002.445870109999</v>
       </c>
-      <c r="I187">
-        <v>6.5188294958562987E-2</v>
+      <c r="I187" s="4">
+        <v>6.5605531730152336E-2</v>
       </c>
       <c r="J187">
         <v>17846.44783605</v>
       </c>
-      <c r="K187">
-        <v>5.4788579696859921E-2</v>
+      <c r="K187" s="4">
+        <v>5.528494521100967E-2</v>
       </c>
       <c r="L187">
         <v>4</v>
@@ -11601,14 +11603,14 @@
       <c r="H188">
         <v>11127.4638713</v>
       </c>
-      <c r="I188">
-        <v>6.5453367221661868E-2</v>
+      <c r="I188" s="4">
+        <v>6.5642488635107785E-2</v>
       </c>
       <c r="J188">
         <v>18080.77838353</v>
       </c>
-      <c r="K188">
-        <v>5.4934086496212002E-2</v>
+      <c r="K188" s="4">
+        <v>5.5291202580117903E-2</v>
       </c>
       <c r="L188">
         <v>3.75</v>
@@ -11642,14 +11644,14 @@
       <c r="H189">
         <v>11257.6521689</v>
       </c>
-      <c r="I189">
-        <v>6.5934446371816072E-2</v>
+      <c r="I189" s="4">
+        <v>6.588634337115136E-2</v>
       </c>
       <c r="J189">
         <v>18294.073296750001</v>
       </c>
-      <c r="K189">
-        <v>5.5067736475134001E-2</v>
+      <c r="K189" s="4">
+        <v>5.5218046901260982E-2</v>
       </c>
       <c r="L189">
         <v>3.75</v>
@@ -11683,14 +11685,14 @@
       <c r="H190">
         <v>11416.66105242</v>
       </c>
-      <c r="I190">
-        <v>6.6247105384074176E-2</v>
+      <c r="I190" s="4">
+        <v>6.6173802823248501E-2</v>
       </c>
       <c r="J190">
         <v>18591.994547769998</v>
       </c>
-      <c r="K190">
-        <v>5.5348235044697311E-2</v>
+      <c r="K190" s="4">
+        <v>5.5517127183606088E-2</v>
       </c>
       <c r="L190">
         <v>3.5</v>
@@ -11724,14 +11726,14 @@
       <c r="H191">
         <v>11578.39890303</v>
       </c>
-      <c r="I191">
-        <v>6.8255587346796945E-2</v>
+      <c r="I191" s="4">
+        <v>6.8115003035270238E-2</v>
       </c>
       <c r="J191">
         <v>18792.029234900001</v>
       </c>
-      <c r="K191">
-        <v>5.7307793343111743E-2</v>
+      <c r="K191" s="4">
+        <v>5.7427673180368372E-2</v>
       </c>
       <c r="L191">
         <v>3.5</v>
@@ -11765,14 +11767,14 @@
       <c r="H192">
         <v>11766.68191992</v>
       </c>
-      <c r="I192">
-        <v>6.927933086674376E-2</v>
+      <c r="I192" s="4">
+        <v>6.9364367354687678E-2</v>
       </c>
       <c r="J192">
         <v>19132.106648050001</v>
       </c>
-      <c r="K192">
-        <v>5.7948136742186858E-2</v>
+      <c r="K192" s="4">
+        <v>5.8142550652727158E-2</v>
       </c>
       <c r="L192">
         <v>3.25</v>
@@ -11806,14 +11808,14 @@
       <c r="H193">
         <v>11848.609286819999</v>
       </c>
-      <c r="I193">
-        <v>7.0267327773744545E-2</v>
+      <c r="I193" s="4">
+        <v>7.0405308414485099E-2</v>
       </c>
       <c r="J193">
         <v>19318.403555860001</v>
       </c>
-      <c r="K193">
-        <v>5.8773540449445043E-2</v>
+      <c r="K193" s="4">
+        <v>5.8905622145337559E-2</v>
       </c>
       <c r="L193">
         <v>3.25</v>
@@ -11847,13 +11849,13 @@
       <c r="H194">
         <v>11831.27228092</v>
       </c>
-      <c r="I194">
+      <c r="I194" s="4">
         <v>6.9551730070234866E-2</v>
       </c>
       <c r="J194">
         <v>19311.82203698</v>
       </c>
-      <c r="K194">
+      <c r="K194" s="4">
         <v>5.7302769182573432E-2</v>
       </c>
       <c r="L194">
@@ -11888,14 +11890,14 @@
       <c r="H195">
         <v>11926.22401939</v>
       </c>
-      <c r="I195">
-        <v>7.054913001473033E-2</v>
+      <c r="I195" s="4">
+        <v>7.0851284573695994E-2</v>
       </c>
       <c r="J195">
         <v>19466.64535789</v>
       </c>
-      <c r="K195">
-        <v>5.8717288648632723E-2</v>
+      <c r="K195" s="4">
+        <v>5.8906521880290497E-2</v>
       </c>
       <c r="L195">
         <v>3</v>
@@ -11929,14 +11931,14 @@
       <c r="H196">
         <v>12008.959167860001</v>
       </c>
-      <c r="I196">
-        <v>7.1909041416609837E-2</v>
+      <c r="I196" s="4">
+        <v>7.2587116349080882E-2</v>
       </c>
       <c r="J196">
         <v>19601.263714069999</v>
       </c>
-      <c r="K196">
-        <v>6.058360528491092E-2</v>
+      <c r="K196" s="4">
+        <v>6.1221031101595443E-2</v>
       </c>
       <c r="L196">
         <v>2.75</v>
@@ -11970,14 +11972,14 @@
       <c r="H197">
         <v>12121.904594170001</v>
       </c>
-      <c r="I197">
-        <v>7.2026393727342236E-2</v>
+      <c r="I197" s="4">
+        <v>7.2642060534175767E-2</v>
       </c>
       <c r="J197">
         <v>19741.307738160001</v>
       </c>
-      <c r="K197">
-        <v>6.1057418135972437E-2</v>
+      <c r="K197" s="4">
+        <v>6.1645097826065053E-2</v>
       </c>
       <c r="L197">
         <v>2.75</v>
@@ -12011,14 +12013,14 @@
       <c r="H198">
         <v>12233.246765280001</v>
       </c>
-      <c r="I198">
-        <v>7.1407280150314209E-2</v>
+      <c r="I198" s="4">
+        <v>7.1906414735335808E-2</v>
       </c>
       <c r="J198">
         <v>19860.186654410001</v>
       </c>
-      <c r="K198">
-        <v>5.9902178226332183E-2</v>
+      <c r="K198" s="4">
+        <v>6.0436068983029237E-2</v>
       </c>
       <c r="L198">
         <v>2.75</v>
@@ -12052,14 +12054,14 @@
       <c r="H199">
         <v>12263.66973541</v>
       </c>
-      <c r="I199">
-        <v>7.391909360696422E-2</v>
+      <c r="I199" s="4">
+        <v>7.433633037855357E-2</v>
       </c>
       <c r="J199">
         <v>19909.127866819999</v>
       </c>
-      <c r="K199">
-        <v>6.2292720596116603E-2</v>
+      <c r="K199" s="4">
+        <v>6.2789086110266346E-2</v>
       </c>
       <c r="L199">
         <v>2.75</v>
@@ -12093,14 +12095,14 @@
       <c r="H200">
         <v>12298.44860055</v>
       </c>
-      <c r="I200">
-        <v>7.3088693320327858E-2</v>
+      <c r="I200" s="4">
+        <v>7.3277814733773775E-2</v>
       </c>
       <c r="J200">
         <v>19952.4820955</v>
       </c>
-      <c r="K200">
-        <v>6.2578825983970077E-2</v>
+      <c r="K200" s="4">
+        <v>6.2935942067875991E-2</v>
       </c>
       <c r="L200">
         <v>2.75</v>
@@ -12134,14 +12136,14 @@
       <c r="H201">
         <v>12379.50053367</v>
       </c>
-      <c r="I201">
-        <v>7.6297081968636299E-2</v>
+      <c r="I201" s="4">
+        <v>7.6248978967971587E-2</v>
       </c>
       <c r="J201">
         <v>20086.543096689998</v>
       </c>
-      <c r="K201">
-        <v>6.5451695266192572E-2</v>
+      <c r="K201" s="4">
+        <v>6.5602005692319554E-2</v>
       </c>
       <c r="L201">
         <v>2.75</v>
@@ -12175,14 +12177,14 @@
       <c r="H202">
         <v>12466.49683412</v>
       </c>
-      <c r="I202">
-        <v>7.7875300919169041E-2</v>
+      <c r="I202" s="4">
+        <v>7.7801998358343366E-2</v>
       </c>
       <c r="J202">
         <v>20267.926000790001</v>
       </c>
-      <c r="K202">
-        <v>6.6762803754305558E-2</v>
+      <c r="K202" s="4">
+        <v>6.6931695893214335E-2</v>
       </c>
       <c r="L202">
         <v>2.75</v>
@@ -12216,14 +12218,14 @@
       <c r="H203">
         <v>12610.14065913</v>
       </c>
-      <c r="I203">
-        <v>7.9274899998765302E-2</v>
+      <c r="I203" s="4">
+        <v>7.9134315687238596E-2</v>
       </c>
       <c r="J203">
         <v>20501.550773080002</v>
       </c>
-      <c r="K203">
-        <v>6.822945181799106E-2</v>
+      <c r="K203" s="4">
+        <v>6.8349331655247703E-2</v>
       </c>
       <c r="L203">
         <v>2.75</v>
@@ -12257,14 +12259,14 @@
       <c r="H204">
         <v>12786.251230809999</v>
       </c>
-      <c r="I204">
-        <v>7.848626097795014E-2</v>
+      <c r="I204" s="4">
+        <v>7.8571297465894058E-2</v>
       </c>
       <c r="J204">
         <v>20775.703495990001</v>
       </c>
-      <c r="K204">
-        <v>6.713651214476106E-2</v>
+      <c r="K204" s="4">
+        <v>6.7330926055301346E-2</v>
       </c>
       <c r="L204">
         <v>2.75</v>
@@ -12298,14 +12300,14 @@
       <c r="H205">
         <v>12916.139207509999</v>
       </c>
-      <c r="I205">
-        <v>8.0015201800105684E-2</v>
+      <c r="I205" s="4">
+        <v>8.0153182440846238E-2</v>
       </c>
       <c r="J205">
         <v>20995.955960210002</v>
       </c>
-      <c r="K205">
-        <v>6.8525372870310186E-2</v>
+      <c r="K205" s="4">
+        <v>6.8657454566202716E-2</v>
       </c>
       <c r="L205">
         <v>2.75</v>
@@ -12339,13 +12341,13 @@
       <c r="H206">
         <v>12915.69829122</v>
       </c>
-      <c r="I206">
+      <c r="I206" s="4">
         <v>7.6551441540882198E-2</v>
       </c>
       <c r="J206">
         <v>21044.601705239998</v>
       </c>
-      <c r="K206">
+      <c r="K206" s="4">
         <v>6.6975108456390986E-2</v>
       </c>
       <c r="L206">
@@ -12380,14 +12382,14 @@
       <c r="H207">
         <v>13055.296494349999</v>
       </c>
-      <c r="I207">
-        <v>7.711822990169169E-2</v>
+      <c r="I207" s="4">
+        <v>7.7420384460657354E-2</v>
       </c>
       <c r="J207">
         <v>21235.663027449998</v>
       </c>
-      <c r="K207">
-        <v>6.8604659525479353E-2</v>
+      <c r="K207" s="4">
+        <v>6.879389275713714E-2</v>
       </c>
       <c r="L207">
         <v>2.75</v>
@@ -12421,14 +12423,14 @@
       <c r="H208">
         <v>13171.104831570001</v>
       </c>
-      <c r="I208">
-        <v>7.5918495965609387E-2</v>
+      <c r="I208" s="4">
+        <v>7.6596570898080432E-2</v>
       </c>
       <c r="J208">
         <v>21431.423828319999</v>
       </c>
-      <c r="K208">
-        <v>6.7848191852750414E-2</v>
+      <c r="K208" s="4">
+        <v>6.8485617669434937E-2</v>
       </c>
       <c r="L208">
         <v>2.75</v>
@@ -12462,14 +12464,14 @@
       <c r="H209">
         <v>13237.62139536</v>
       </c>
-      <c r="I209">
-        <v>7.5543328773418073E-2</v>
+      <c r="I209" s="4">
+        <v>7.6158995580251604E-2</v>
       </c>
       <c r="J209">
         <v>21522.610524750002</v>
       </c>
-      <c r="K209">
-        <v>6.8346088106633771E-2</v>
+      <c r="K209" s="4">
+        <v>6.8933767796726386E-2</v>
       </c>
       <c r="L209">
         <v>2.75</v>
@@ -12503,14 +12505,14 @@
       <c r="H210">
         <v>13399.05141362</v>
       </c>
-      <c r="I210">
-        <v>7.4867152834848405E-2</v>
+      <c r="I210" s="4">
+        <v>7.5366287419870004E-2</v>
       </c>
       <c r="J210">
         <v>21732.564350469998</v>
       </c>
-      <c r="K210">
-        <v>6.7089384215781311E-2</v>
+      <c r="K210" s="4">
+        <v>6.7623274972478373E-2</v>
       </c>
       <c r="L210">
         <v>2.75</v>
@@ -12544,14 +12546,14 @@
       <c r="H211">
         <v>13481.76974811</v>
       </c>
-      <c r="I211">
-        <v>7.5185980958787479E-2</v>
+      <c r="I211" s="4">
+        <v>7.5603217730376829E-2</v>
       </c>
       <c r="J211">
         <v>21845.19135325</v>
       </c>
-      <c r="K211">
-        <v>6.5971140471461465E-2</v>
+      <c r="K211" s="4">
+        <v>6.6467505985611214E-2</v>
       </c>
       <c r="L211">
         <v>2.75</v>
@@ -12585,14 +12587,14 @@
       <c r="H212">
         <v>13605.61360875</v>
       </c>
-      <c r="I212">
-        <v>7.666429178832071E-2</v>
+      <c r="I212" s="4">
+        <v>7.6853413201766627E-2</v>
       </c>
       <c r="J212">
         <v>21960.85232242</v>
       </c>
-      <c r="K212">
-        <v>6.728829996071789E-2</v>
+      <c r="K212" s="4">
+        <v>6.7645416044623805E-2</v>
       </c>
       <c r="L212">
         <v>2.75</v>
@@ -12626,14 +12628,14 @@
       <c r="H213">
         <v>13745.13069692</v>
       </c>
-      <c r="I213">
-        <v>7.6916296495942685E-2</v>
+      <c r="I213" s="4">
+        <v>7.6868193495277973E-2</v>
       </c>
       <c r="J213">
         <v>22196.32818221</v>
       </c>
-      <c r="K213">
-        <v>6.8143514631472557E-2</v>
+      <c r="K213" s="4">
+        <v>6.8293825057599539E-2</v>
       </c>
       <c r="L213">
         <v>2.5</v>
@@ -12667,14 +12669,14 @@
       <c r="H214">
         <v>13850.034324</v>
       </c>
-      <c r="I214">
-        <v>7.6952204714297062E-2</v>
+      <c r="I214" s="4">
+        <v>7.6878902153471387E-2</v>
       </c>
       <c r="J214">
         <v>22334.13241287</v>
       </c>
-      <c r="K214">
-        <v>6.8180793507375922E-2</v>
+      <c r="K214" s="4">
+        <v>6.83496856462847E-2</v>
       </c>
       <c r="L214">
         <v>2.5</v>
@@ -12708,14 +12710,14 @@
       <c r="H215">
         <v>14071.466916949999</v>
       </c>
-      <c r="I215">
-        <v>7.735721110618074E-2</v>
+      <c r="I215" s="4">
+        <v>7.7216626794654034E-2</v>
       </c>
       <c r="J215">
         <v>22629.592642719999</v>
       </c>
-      <c r="K215">
-        <v>6.8614476362490615E-2</v>
+      <c r="K215" s="4">
+        <v>6.8734356199747257E-2</v>
       </c>
       <c r="L215">
         <v>2.5</v>
@@ -12749,14 +12751,14 @@
       <c r="H216">
         <v>14350.546841380001</v>
       </c>
-      <c r="I216">
-        <v>7.9513602870081912E-2</v>
+      <c r="I216" s="4">
+        <v>7.959863935802583E-2</v>
       </c>
       <c r="J216">
         <v>22979.230807510001</v>
       </c>
-      <c r="K216">
-        <v>7.008687691708422E-2</v>
+      <c r="K216" s="4">
+        <v>7.0281290827624507E-2</v>
       </c>
       <c r="L216">
         <v>2.25</v>
@@ -12790,14 +12792,14 @@
       <c r="H217">
         <v>14482.16809841</v>
       </c>
-      <c r="I217">
-        <v>8.0972261920641761E-2</v>
+      <c r="I217" s="4">
+        <v>8.1110242561382315E-2</v>
       </c>
       <c r="J217">
         <v>23211.904604250001</v>
       </c>
-      <c r="K217">
-        <v>7.2365091527655773E-2</v>
+      <c r="K217" s="4">
+        <v>7.2497173223548303E-2</v>
       </c>
       <c r="L217">
         <v>2.25</v>
@@ -12831,13 +12833,13 @@
       <c r="H218">
         <v>14543.92518627</v>
       </c>
-      <c r="I218">
+      <c r="I218" s="4">
         <v>7.9046539975006824E-2</v>
       </c>
       <c r="J218">
         <v>23285.579884980001</v>
       </c>
-      <c r="K218">
+      <c r="K218" s="4">
         <v>7.0956369877898759E-2</v>
       </c>
       <c r="L218">
@@ -12872,1414 +12874,20 @@
       <c r="H219">
         <v>14643.50945086</v>
       </c>
-      <c r="I219">
-        <v>7.7453652464489514E-2</v>
+      <c r="I219" s="4">
+        <v>7.7755807023455178E-2</v>
       </c>
       <c r="J219">
         <v>23449.600949539999</v>
       </c>
-      <c r="K219">
-        <v>6.9414799517703657E-2</v>
+      <c r="K219" s="4">
+        <v>6.9604032749361444E-2</v>
       </c>
       <c r="L219">
         <v>2.25</v>
       </c>
       <c r="M219">
         <v>173.35146690051599</v>
-      </c>
-    </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A220" s="2">
-        <v>43891</v>
-      </c>
-      <c r="B220">
-        <v>2159.4283639800001</v>
-      </c>
-      <c r="C220">
-        <v>0.12695874925191039</v>
-      </c>
-      <c r="D220">
-        <v>4956.9658562300001</v>
-      </c>
-      <c r="E220">
-        <v>3.6257077842107473E-2</v>
-      </c>
-      <c r="F220">
-        <v>1443.19440762</v>
-      </c>
-      <c r="G220">
-        <v>3.5151683087284828E-2</v>
-      </c>
-      <c r="H220">
-        <v>14310.29253604</v>
-      </c>
-      <c r="I220">
-        <v>7.6405917177009994E-2</v>
-      </c>
-      <c r="J220">
-        <v>22869.881163869999</v>
-      </c>
-      <c r="K220">
-        <v>6.9744040935945037E-2</v>
-      </c>
-      <c r="L220">
-        <v>1.25</v>
-      </c>
-      <c r="M220">
-        <v>140.82045052103899</v>
-      </c>
-    </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A221" s="2">
-        <v>43922</v>
-      </c>
-      <c r="B221">
-        <v>2138.9006645700001</v>
-      </c>
-      <c r="C221">
-        <v>0.1174060293540956</v>
-      </c>
-      <c r="D221">
-        <v>4833.40990616</v>
-      </c>
-      <c r="E221">
-        <v>3.6674382661831727E-2</v>
-      </c>
-      <c r="F221">
-        <v>1435.3239125</v>
-      </c>
-      <c r="G221">
-        <v>3.6710352026549972E-2</v>
-      </c>
-      <c r="H221">
-        <v>14089.046786409999</v>
-      </c>
-      <c r="I221">
-        <v>7.5415437457299686E-2</v>
-      </c>
-      <c r="J221">
-        <v>22496.681269640001</v>
-      </c>
-      <c r="K221">
-        <v>6.8471206479831084E-2</v>
-      </c>
-      <c r="L221">
-        <v>0.25</v>
-      </c>
-      <c r="M221">
-        <v>104.571783804586</v>
-      </c>
-    </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A222" s="2">
-        <v>43952</v>
-      </c>
-      <c r="B222">
-        <v>2183.1003610900002</v>
-      </c>
-      <c r="C222">
-        <v>0.1124785327905852</v>
-      </c>
-      <c r="D222">
-        <v>4733.6882485699998</v>
-      </c>
-      <c r="E222">
-        <v>3.7745282498055449E-2</v>
-      </c>
-      <c r="F222">
-        <v>1428.6810697999999</v>
-      </c>
-      <c r="G222">
-        <v>3.6032640088950393E-2</v>
-      </c>
-      <c r="H222">
-        <v>14087.11798673</v>
-      </c>
-      <c r="I222">
-        <v>7.4352098866691738E-2</v>
-      </c>
-      <c r="J222">
-        <v>22432.58766619</v>
-      </c>
-      <c r="K222">
-        <v>6.7608514397507119E-2</v>
-      </c>
-      <c r="L222">
-        <v>0.25</v>
-      </c>
-      <c r="M222">
-        <v>116.20409231795</v>
-      </c>
-    </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A223" s="2">
-        <v>43983</v>
-      </c>
-      <c r="B223">
-        <v>2204.0703212399999</v>
-      </c>
-      <c r="C223">
-        <v>0.11094637160779269</v>
-      </c>
-      <c r="D223">
-        <v>4646.4947893199997</v>
-      </c>
-      <c r="E223">
-        <v>3.8160728975217321E-2</v>
-      </c>
-      <c r="F223">
-        <v>1420.3440982899999</v>
-      </c>
-      <c r="G223">
-        <v>3.7407814911870563E-2</v>
-      </c>
-      <c r="H223">
-        <v>14248.5252177</v>
-      </c>
-      <c r="I223">
-        <v>7.426830870131311E-2</v>
-      </c>
-      <c r="J223">
-        <v>22519.43442655</v>
-      </c>
-      <c r="K223">
-        <v>6.8222768015602397E-2</v>
-      </c>
-      <c r="L223">
-        <v>0.25</v>
-      </c>
-      <c r="M223">
-        <v>139.91102445364899</v>
-      </c>
-    </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A224" s="2">
-        <v>44013</v>
-      </c>
-      <c r="B224">
-        <v>2217.3487439099999</v>
-      </c>
-      <c r="C224">
-        <v>0.1156340769146989</v>
-      </c>
-      <c r="D224">
-        <v>4608.5607300699994</v>
-      </c>
-      <c r="E224">
-        <v>3.4936834461017169E-2</v>
-      </c>
-      <c r="F224">
-        <v>1409.0320153600001</v>
-      </c>
-      <c r="G224">
-        <v>3.6914573482356793E-2</v>
-      </c>
-      <c r="H224">
-        <v>14932.27259633</v>
-      </c>
-      <c r="I224">
-        <v>6.6553403465227964E-2</v>
-      </c>
-      <c r="J224">
-        <v>23167.214085669999</v>
-      </c>
-      <c r="K224">
-        <v>6.2919308120480313E-2</v>
-      </c>
-      <c r="L224">
-        <v>0.25</v>
-      </c>
-      <c r="M224">
-        <v>152.544198892754</v>
-      </c>
-    </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A225" s="2">
-        <v>44044</v>
-      </c>
-      <c r="B225">
-        <v>2261.7211269300001</v>
-      </c>
-      <c r="C225">
-        <v>0.11143274656150851</v>
-      </c>
-      <c r="D225">
-        <v>4619.2933561999998</v>
-      </c>
-      <c r="E225">
-        <v>3.2603356746732523E-2</v>
-      </c>
-      <c r="F225">
-        <v>1401.97957561</v>
-      </c>
-      <c r="G225">
-        <v>3.6528284449306427E-2</v>
-      </c>
-      <c r="H225">
-        <v>15448.824612799999</v>
-      </c>
-      <c r="I225">
-        <v>6.2766093787860758E-2</v>
-      </c>
-      <c r="J225">
-        <v>23731.818671540001</v>
-      </c>
-      <c r="K225">
-        <v>6.00026305235625E-2</v>
-      </c>
-      <c r="L225">
-        <v>0.25</v>
-      </c>
-      <c r="M225">
-        <v>156.36406569440399</v>
-      </c>
-    </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A226" s="2">
-        <v>44075</v>
-      </c>
-      <c r="B226">
-        <v>2276.9921576400002</v>
-      </c>
-      <c r="C226">
-        <v>0.11070809773946309</v>
-      </c>
-      <c r="D226">
-        <v>4673.3158472900004</v>
-      </c>
-      <c r="E226">
-        <v>3.0915695022792341E-2</v>
-      </c>
-      <c r="F226">
-        <v>1403.2395340800001</v>
-      </c>
-      <c r="G226">
-        <v>4.1048794386886259E-2</v>
-      </c>
-      <c r="H226">
-        <v>16164.727005320001</v>
-      </c>
-      <c r="I226">
-        <v>6.017986948882903E-2</v>
-      </c>
-      <c r="J226">
-        <v>24518.274544330001</v>
-      </c>
-      <c r="K226">
-        <v>5.864331103308755E-2</v>
-      </c>
-      <c r="L226">
-        <v>0.25</v>
-      </c>
-      <c r="M226">
-        <v>160.26131398211101</v>
-      </c>
-    </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A227" s="2">
-        <v>44105</v>
-      </c>
-      <c r="B227">
-        <v>2231.4262205499999</v>
-      </c>
-      <c r="C227">
-        <v>0.10771210436917709</v>
-      </c>
-      <c r="D227">
-        <v>4806.8549881299996</v>
-      </c>
-      <c r="E227">
-        <v>3.1291336042262183E-2</v>
-      </c>
-      <c r="F227">
-        <v>1404.1004755700001</v>
-      </c>
-      <c r="G227">
-        <v>4.3559165860385649E-2</v>
-      </c>
-      <c r="H227">
-        <v>16643.936121160001</v>
-      </c>
-      <c r="I227">
-        <v>5.5730837191919069E-2</v>
-      </c>
-      <c r="J227">
-        <v>25086.317805409999</v>
-      </c>
-      <c r="K227">
-        <v>5.547551112428134E-2</v>
-      </c>
-      <c r="L227">
-        <v>0.25</v>
-      </c>
-      <c r="M227">
-        <v>166.74684518517901</v>
-      </c>
-    </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A228" s="2">
-        <v>44136</v>
-      </c>
-      <c r="B228">
-        <v>2280.1507402299999</v>
-      </c>
-      <c r="C228">
-        <v>0.10319941129693209</v>
-      </c>
-      <c r="D228">
-        <v>4948.6570592999997</v>
-      </c>
-      <c r="E228">
-        <v>3.0511784985431639E-2</v>
-      </c>
-      <c r="F228">
-        <v>1409.1993044200001</v>
-      </c>
-      <c r="G228">
-        <v>4.370211886766949E-2</v>
-      </c>
-      <c r="H228">
-        <v>17039.103716760001</v>
-      </c>
-      <c r="I228">
-        <v>5.5228463543846702E-2</v>
-      </c>
-      <c r="J228">
-        <v>25677.110820710001</v>
-      </c>
-      <c r="K228">
-        <v>5.4646923515431163E-2</v>
-      </c>
-      <c r="L228">
-        <v>0.25</v>
-      </c>
-      <c r="M228">
-        <v>168.292170423214</v>
-      </c>
-    </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A229" s="2">
-        <v>44166</v>
-      </c>
-      <c r="B229">
-        <v>2300.3196402100002</v>
-      </c>
-      <c r="C229">
-        <v>0.101678955690109</v>
-      </c>
-      <c r="D229">
-        <v>5069.7182674599999</v>
-      </c>
-      <c r="E229">
-        <v>2.6994189913548239E-2</v>
-      </c>
-      <c r="F229">
-        <v>1416.1758750700001</v>
-      </c>
-      <c r="G229">
-        <v>4.279667385027601E-2</v>
-      </c>
-      <c r="H229">
-        <v>17303.47789563</v>
-      </c>
-      <c r="I229">
-        <v>5.5811118977760393E-2</v>
-      </c>
-      <c r="J229">
-        <v>26089.69167837</v>
-      </c>
-      <c r="K229">
-        <v>5.4856669325880313E-2</v>
-      </c>
-      <c r="L229">
-        <v>0.25</v>
-      </c>
-      <c r="M229">
-        <v>172.400120770981</v>
-      </c>
-    </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A230" s="2">
-        <v>44197</v>
-      </c>
-      <c r="B230">
-        <v>2275.7306163899998</v>
-      </c>
-      <c r="C230">
-        <v>0.1052414975766867</v>
-      </c>
-      <c r="D230">
-        <v>5112.7377065800001</v>
-      </c>
-      <c r="E230">
-        <v>2.6677292383777761E-2</v>
-      </c>
-      <c r="F230">
-        <v>1409.5821437</v>
-      </c>
-      <c r="G230">
-        <v>4.2525803819176179E-2</v>
-      </c>
-      <c r="H230">
-        <v>17303.545139239999</v>
-      </c>
-      <c r="I230">
-        <v>5.1406725220879752E-2</v>
-      </c>
-      <c r="J230">
-        <v>26101.595605909999</v>
-      </c>
-      <c r="K230">
-        <v>5.0776876665727999E-2</v>
-      </c>
-      <c r="L230">
-        <v>0.25</v>
-      </c>
-      <c r="M230">
-        <v>172.90099314200501</v>
-      </c>
-    </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A231" s="2">
-        <v>44228</v>
-      </c>
-      <c r="B231">
-        <v>2279.78727114</v>
-      </c>
-      <c r="C231">
-        <v>0.1030168990515333</v>
-      </c>
-      <c r="D231">
-        <v>5152.0684472299999</v>
-      </c>
-      <c r="E231">
-        <v>2.6486224526649459E-2</v>
-      </c>
-      <c r="F231">
-        <v>1410.2242385100001</v>
-      </c>
-      <c r="G231">
-        <v>4.2750860993354352E-2</v>
-      </c>
-      <c r="H231">
-        <v>17292.186950200001</v>
-      </c>
-      <c r="I231">
-        <v>5.6515195110583193E-2</v>
-      </c>
-      <c r="J231">
-        <v>26134.26690708</v>
-      </c>
-      <c r="K231">
-        <v>5.3860786025919857E-2</v>
-      </c>
-      <c r="L231">
-        <v>0.25</v>
-      </c>
-      <c r="M231">
-        <v>169.15538756642201</v>
-      </c>
-    </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A232" s="2">
-        <v>44256</v>
-      </c>
-      <c r="B232">
-        <v>2271.0733725499999</v>
-      </c>
-      <c r="C232">
-        <v>9.826505070570403E-2</v>
-      </c>
-      <c r="D232">
-        <v>5229.7713057399997</v>
-      </c>
-      <c r="E232">
-        <v>2.6958617246849309E-2</v>
-      </c>
-      <c r="F232">
-        <v>1410.99503755</v>
-      </c>
-      <c r="G232">
-        <v>4.2955943746791667E-2</v>
-      </c>
-      <c r="H232">
-        <v>17410.84239396</v>
-      </c>
-      <c r="I232">
-        <v>6.1272067265878867E-2</v>
-      </c>
-      <c r="J232">
-        <v>26322.6821098</v>
-      </c>
-      <c r="K232">
-        <v>5.6629337648931077E-2</v>
-      </c>
-      <c r="L232">
-        <v>0.25</v>
-      </c>
-      <c r="M232">
-        <v>168.75683535705301</v>
-      </c>
-    </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A233" s="2">
-        <v>44287</v>
-      </c>
-      <c r="B233">
-        <v>2280.2364451200001</v>
-      </c>
-      <c r="C233">
-        <v>9.9853541937409723E-2</v>
-      </c>
-      <c r="D233">
-        <v>5299.7645609700003</v>
-      </c>
-      <c r="E233">
-        <v>2.8025877446302049E-2</v>
-      </c>
-      <c r="F233">
-        <v>1414.0914274300001</v>
-      </c>
-      <c r="G233">
-        <v>4.3759021969647802E-2</v>
-      </c>
-      <c r="H233">
-        <v>17590.599337340002</v>
-      </c>
-      <c r="I233">
-        <v>6.1999906928981073E-2</v>
-      </c>
-      <c r="J233">
-        <v>26584.691770860001</v>
-      </c>
-      <c r="K233">
-        <v>5.7505229116763812E-2</v>
-      </c>
-      <c r="L233">
-        <v>0.25</v>
-      </c>
-      <c r="M233">
-        <v>167.832160638837</v>
-      </c>
-    </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A234" s="2">
-        <v>44317</v>
-      </c>
-      <c r="B234">
-        <v>2276.4251643399998</v>
-      </c>
-      <c r="C234">
-        <v>9.7517738785127928E-2</v>
-      </c>
-      <c r="D234">
-        <v>5333.5101946000004</v>
-      </c>
-      <c r="E234">
-        <v>3.2891037969255521E-2</v>
-      </c>
-      <c r="F234">
-        <v>1414.1026799700001</v>
-      </c>
-      <c r="G234">
-        <v>4.5129050290289997E-2</v>
-      </c>
-      <c r="H234">
-        <v>17861.444640760001</v>
-      </c>
-      <c r="I234">
-        <v>6.2341615703127802E-2</v>
-      </c>
-      <c r="J234">
-        <v>26885.48267967</v>
-      </c>
-      <c r="K234">
-        <v>5.8441697281614129E-2</v>
-      </c>
-      <c r="L234">
-        <v>0.25</v>
-      </c>
-      <c r="M234">
-        <v>172.46262082341099</v>
-      </c>
-    </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A235" s="2">
-        <v>44348</v>
-      </c>
-      <c r="B235">
-        <v>2286.9315393799998</v>
-      </c>
-      <c r="C235">
-        <v>9.1658109978590793E-2</v>
-      </c>
-      <c r="D235">
-        <v>5358.6517146100005</v>
-      </c>
-      <c r="E235">
-        <v>3.1368390944630307E-2</v>
-      </c>
-      <c r="F235">
-        <v>1408.03971073</v>
-      </c>
-      <c r="G235">
-        <v>4.4266246424034192E-2</v>
-      </c>
-      <c r="H235">
-        <v>18024.676300989999</v>
-      </c>
-      <c r="I235">
-        <v>5.9752386877485048E-2</v>
-      </c>
-      <c r="J235">
-        <v>27078.29926571</v>
-      </c>
-      <c r="K235">
-        <v>5.6260746439557287E-2</v>
-      </c>
-      <c r="L235">
-        <v>0.25</v>
-      </c>
-      <c r="M235">
-        <v>172.756272866323</v>
-      </c>
-    </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A236" s="2">
-        <v>44378</v>
-      </c>
-      <c r="B236">
-        <v>2262.2419197999998</v>
-      </c>
-      <c r="C236">
-        <v>9.8105483802378254E-2</v>
-      </c>
-      <c r="D236">
-        <v>5368.7611469200001</v>
-      </c>
-      <c r="E236">
-        <v>3.2271793767431257E-2</v>
-      </c>
-      <c r="F236">
-        <v>1409.3347980000001</v>
-      </c>
-      <c r="G236">
-        <v>4.3749786947359537E-2</v>
-      </c>
-      <c r="H236">
-        <v>18214.69351021</v>
-      </c>
-      <c r="I236">
-        <v>6.1709936695100623E-2</v>
-      </c>
-      <c r="J236">
-        <v>27255.03137493</v>
-      </c>
-      <c r="K236">
-        <v>5.7844933741875118E-2</v>
-      </c>
-      <c r="L236">
-        <v>0.25</v>
-      </c>
-      <c r="M236">
-        <v>173.54042175974399</v>
-      </c>
-    </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A237" s="2">
-        <v>44409</v>
-      </c>
-      <c r="B237">
-        <v>2234.4294547300001</v>
-      </c>
-      <c r="C237">
-        <v>9.8231403616420049E-2</v>
-      </c>
-      <c r="D237">
-        <v>5406.58861299</v>
-      </c>
-      <c r="E237">
-        <v>3.0962517930030201E-2</v>
-      </c>
-      <c r="F237">
-        <v>1274.8114010700001</v>
-      </c>
-      <c r="G237">
-        <v>3.31111587287116E-2</v>
-      </c>
-      <c r="H237">
-        <v>18427.78186173</v>
-      </c>
-      <c r="I237">
-        <v>5.9889314619637118E-2</v>
-      </c>
-      <c r="J237">
-        <v>27343.611330520002</v>
-      </c>
-      <c r="K237">
-        <v>5.6145973649776762E-2</v>
-      </c>
-      <c r="L237">
-        <v>0.5</v>
-      </c>
-      <c r="M237">
-        <v>174.87920486451901</v>
-      </c>
-    </row>
-    <row r="238" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A238" s="2">
-        <v>44440</v>
-      </c>
-      <c r="B238">
-        <v>2202.2242701199998</v>
-      </c>
-      <c r="C238">
-        <v>0.1005012039976927</v>
-      </c>
-      <c r="D238">
-        <v>5473.4202434999997</v>
-      </c>
-      <c r="E238">
-        <v>3.062295816570073E-2</v>
-      </c>
-      <c r="F238">
-        <v>1277.1083010699999</v>
-      </c>
-      <c r="G238">
-        <v>3.2102560257145203E-2</v>
-      </c>
-      <c r="H238">
-        <v>18797.73941237</v>
-      </c>
-      <c r="I238">
-        <v>5.9203044509666902E-2</v>
-      </c>
-      <c r="J238">
-        <v>27750.49222706</v>
-      </c>
-      <c r="K238">
-        <v>5.607561073138858E-2</v>
-      </c>
-      <c r="L238">
-        <v>1</v>
-      </c>
-      <c r="M238">
-        <v>175.854950933071</v>
-      </c>
-    </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A239" s="2">
-        <v>44470</v>
-      </c>
-      <c r="B239">
-        <v>2194.2493606399998</v>
-      </c>
-      <c r="C239">
-        <v>0.1004161101114477</v>
-      </c>
-      <c r="D239">
-        <v>5571.17602627</v>
-      </c>
-      <c r="E239">
-        <v>2.930325374753975E-2</v>
-      </c>
-      <c r="F239">
-        <v>1285.5089196199999</v>
-      </c>
-      <c r="G239">
-        <v>3.1440552673837073E-2</v>
-      </c>
-      <c r="H239">
-        <v>19083.164364209999</v>
-      </c>
-      <c r="I239">
-        <v>5.9528650349525883E-2</v>
-      </c>
-      <c r="J239">
-        <v>28134.098670740001</v>
-      </c>
-      <c r="K239">
-        <v>5.5961465093607811E-2</v>
-      </c>
-      <c r="L239">
-        <v>1.5</v>
-      </c>
-      <c r="M239">
-        <v>175.023326475673</v>
-      </c>
-    </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A240" s="2">
-        <v>44501</v>
-      </c>
-      <c r="B240">
-        <v>2172.2655704700001</v>
-      </c>
-      <c r="C240">
-        <v>9.8535122012585449E-2</v>
-      </c>
-      <c r="D240">
-        <v>5670.17393722</v>
-      </c>
-      <c r="E240">
-        <v>2.8580077620943781E-2</v>
-      </c>
-      <c r="F240">
-        <v>1300.8241159700001</v>
-      </c>
-      <c r="G240">
-        <v>3.1301938325180197E-2</v>
-      </c>
-      <c r="H240">
-        <v>19422.658219389999</v>
-      </c>
-      <c r="I240">
-        <v>6.004569223128834E-2</v>
-      </c>
-      <c r="J240">
-        <v>28565.92184305</v>
-      </c>
-      <c r="K240">
-        <v>5.5962434010417797E-2</v>
-      </c>
-      <c r="L240">
-        <v>2</v>
-      </c>
-      <c r="M240">
-        <v>174.28334484974999</v>
-      </c>
-    </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A241" s="2">
-        <v>44531</v>
-      </c>
-      <c r="B241">
-        <v>2169.81716056</v>
-      </c>
-      <c r="C241">
-        <v>9.1217174736012499E-2</v>
-      </c>
-      <c r="D241">
-        <v>5749.7459773599994</v>
-      </c>
-      <c r="E241">
-        <v>2.502358037668688E-2</v>
-      </c>
-      <c r="F241">
-        <v>1388.26564278</v>
-      </c>
-      <c r="G241">
-        <v>2.809212703118107E-2</v>
-      </c>
-      <c r="H241">
-        <v>19628.150631429999</v>
-      </c>
-      <c r="I241">
-        <v>6.021726288427684E-2</v>
-      </c>
-      <c r="J241">
-        <v>28935.97941213</v>
-      </c>
-      <c r="K241">
-        <v>5.5223889091702477E-2</v>
-      </c>
-      <c r="L241">
-        <v>2.5</v>
-      </c>
-      <c r="M241">
-        <v>175.225814954611</v>
-      </c>
-    </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A242" s="2">
-        <v>44562</v>
-      </c>
-      <c r="B242">
-        <v>2163.45077055</v>
-      </c>
-      <c r="C242">
-        <v>9.3923785091879819E-2</v>
-      </c>
-      <c r="D242">
-        <v>5802.8133554100004</v>
-      </c>
-      <c r="E242">
-        <v>2.7455609970888549E-2</v>
-      </c>
-      <c r="F242">
-        <v>1385.66927007</v>
-      </c>
-      <c r="G242">
-        <v>2.9273104979769728E-2</v>
-      </c>
-      <c r="H242">
-        <v>19591.822615789999</v>
-      </c>
-      <c r="I242">
-        <v>5.9054299032267298E-2</v>
-      </c>
-      <c r="J242">
-        <v>28943.756011820002</v>
-      </c>
-      <c r="K242">
-        <v>5.389982758847553E-2</v>
-      </c>
-      <c r="L242">
-        <v>3</v>
-      </c>
-      <c r="M242">
-        <v>177.77595236253299</v>
-      </c>
-    </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A243" s="2">
-        <v>44593</v>
-      </c>
-      <c r="B243">
-        <v>2159.5255895599998</v>
-      </c>
-      <c r="C243">
-        <v>9.7333164277449757E-2</v>
-      </c>
-      <c r="D243">
-        <v>5914.4869055199997</v>
-      </c>
-      <c r="E243">
-        <v>2.795292140822898E-2</v>
-      </c>
-      <c r="F243">
-        <v>1394.5299547</v>
-      </c>
-      <c r="G243">
-        <v>2.907100487398372E-2</v>
-      </c>
-      <c r="H243">
-        <v>19819.768310349999</v>
-      </c>
-      <c r="I243">
-        <v>5.8916916801158348E-2</v>
-      </c>
-      <c r="J243">
-        <v>29288.31076013</v>
-      </c>
-      <c r="K243">
-        <v>5.4057915490261052E-2</v>
-      </c>
-      <c r="L243">
-        <v>3.5</v>
-      </c>
-      <c r="M243">
-        <v>177.45500302739299</v>
-      </c>
-    </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A244" s="2">
-        <v>44621</v>
-      </c>
-      <c r="B244">
-        <v>2154.9887514900001</v>
-      </c>
-      <c r="C244">
-        <v>9.9443574817654645E-2</v>
-      </c>
-      <c r="D244">
-        <v>6025.3310061599996</v>
-      </c>
-      <c r="E244">
-        <v>2.7902767824393208E-2</v>
-      </c>
-      <c r="F244">
-        <v>1402.4647080100001</v>
-      </c>
-      <c r="G244">
-        <v>2.8875945946235711E-2</v>
-      </c>
-      <c r="H244">
-        <v>20139.74479144</v>
-      </c>
-      <c r="I244">
-        <v>5.8641837909758507E-2</v>
-      </c>
-      <c r="J244">
-        <v>29722.529257099999</v>
-      </c>
-      <c r="K244">
-        <v>5.3971710326465507E-2</v>
-      </c>
-      <c r="L244">
-        <v>4</v>
-      </c>
-      <c r="M244">
-        <v>175.624506747689</v>
-      </c>
-    </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A245" s="2">
-        <v>44652</v>
-      </c>
-      <c r="B245">
-        <v>2160.2823818900001</v>
-      </c>
-      <c r="C245">
-        <v>0.10388968486779419</v>
-      </c>
-      <c r="D245">
-        <v>6109.3115564</v>
-      </c>
-      <c r="E245">
-        <v>2.7698388439975741E-2</v>
-      </c>
-      <c r="F245">
-        <v>1409.32815132</v>
-      </c>
-      <c r="G245">
-        <v>2.899783176240598E-2</v>
-      </c>
-      <c r="H245">
-        <v>20322.691519280001</v>
-      </c>
-      <c r="I245">
-        <v>5.7064794004497363E-2</v>
-      </c>
-      <c r="J245">
-        <v>30001.613608889998</v>
-      </c>
-      <c r="K245">
-        <v>5.320409537187834E-2</v>
-      </c>
-      <c r="L245">
-        <v>4.5</v>
-      </c>
-      <c r="M245">
-        <v>175.36384503404199</v>
-      </c>
-    </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A246" s="2">
-        <v>44682</v>
-      </c>
-      <c r="B246">
-        <v>2154.5626099599999</v>
-      </c>
-      <c r="C246">
-        <v>0.1014939018476979</v>
-      </c>
-      <c r="D246">
-        <v>6210.7306745899996</v>
-      </c>
-      <c r="E246">
-        <v>2.7251930952741449E-2</v>
-      </c>
-      <c r="F246">
-        <v>1469.05325739</v>
-      </c>
-      <c r="G246">
-        <v>4.2067353759383641E-2</v>
-      </c>
-      <c r="H246">
-        <v>20483.47195363</v>
-      </c>
-      <c r="I246">
-        <v>5.4972506127947053E-2</v>
-      </c>
-      <c r="J246">
-        <v>30317.818495570002</v>
-      </c>
-      <c r="K246">
-        <v>5.1892990824017937E-2</v>
-      </c>
-      <c r="L246">
-        <v>5</v>
-      </c>
-      <c r="M246">
-        <v>176.549094020246</v>
-      </c>
-    </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A247" s="2">
-        <v>44713</v>
-      </c>
-      <c r="B247">
-        <v>2171.5867223400001</v>
-      </c>
-      <c r="C247">
-        <v>0.1021520059079033</v>
-      </c>
-      <c r="D247">
-        <v>6276.0739399699996</v>
-      </c>
-      <c r="E247">
-        <v>2.6874319215048351E-2</v>
-      </c>
-      <c r="F247">
-        <v>1473.95082613</v>
-      </c>
-      <c r="G247">
-        <v>4.1859331021236047E-2</v>
-      </c>
-      <c r="H247">
-        <v>20658.609303699999</v>
-      </c>
-      <c r="I247">
-        <v>5.5455026776792322E-2</v>
-      </c>
-      <c r="J247">
-        <v>30580.22079214</v>
-      </c>
-      <c r="K247">
-        <v>5.2515106017914599E-2</v>
-      </c>
-      <c r="L247">
-        <v>5.5</v>
-      </c>
-      <c r="M247">
-        <v>179.22937448249701</v>
-      </c>
-    </row>
-    <row r="248" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A248" s="2">
-        <v>44743</v>
-      </c>
-      <c r="B248">
-        <v>2167.5417105699999</v>
-      </c>
-      <c r="C248">
-        <v>0.1105223508372544</v>
-      </c>
-      <c r="D248">
-        <v>6331.3028230299997</v>
-      </c>
-      <c r="E248">
-        <v>2.7757695861701681E-2</v>
-      </c>
-      <c r="F248">
-        <v>1477.4233848900001</v>
-      </c>
-      <c r="G248">
-        <v>4.1208457787158252E-2</v>
-      </c>
-      <c r="H248">
-        <v>20863.02957418</v>
-      </c>
-      <c r="I248">
-        <v>5.638996804828432E-2</v>
-      </c>
-      <c r="J248">
-        <v>30839.297492670001</v>
-      </c>
-      <c r="K248">
-        <v>5.3458761202114131E-2</v>
-      </c>
-      <c r="L248">
-        <v>6</v>
-      </c>
-      <c r="M248">
-        <v>177.76735736691001</v>
-      </c>
-    </row>
-    <row r="249" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A249" s="2">
-        <v>44774</v>
-      </c>
-      <c r="B249">
-        <v>2183.1975619300001</v>
-      </c>
-      <c r="C249">
-        <v>0.11121653208761929</v>
-      </c>
-      <c r="D249">
-        <v>6404.7049425300002</v>
-      </c>
-      <c r="E249">
-        <v>2.750088030915953E-2</v>
-      </c>
-      <c r="F249">
-        <v>1487.36756025</v>
-      </c>
-      <c r="G249">
-        <v>4.0985748815009493E-2</v>
-      </c>
-      <c r="H249">
-        <v>21115.346774969999</v>
-      </c>
-      <c r="I249">
-        <v>5.7011522646728777E-2</v>
-      </c>
-      <c r="J249">
-        <v>31190.616839679999</v>
-      </c>
-      <c r="K249">
-        <v>5.4082769386895879E-2</v>
-      </c>
-      <c r="L249">
-        <v>6.5</v>
-      </c>
-      <c r="M249">
-        <v>177.59760674853001</v>
-      </c>
-    </row>
-    <row r="250" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A250" s="2">
-        <v>44805</v>
-      </c>
-      <c r="B250">
-        <v>2199.7633651400001</v>
-      </c>
-      <c r="C250">
-        <v>0.10735566742424139</v>
-      </c>
-      <c r="D250">
-        <v>6489.5910629800001</v>
-      </c>
-      <c r="E250">
-        <v>2.7683018923153009E-2</v>
-      </c>
-      <c r="F250">
-        <v>1497.1359020499999</v>
-      </c>
-      <c r="G250">
-        <v>3.972146793659212E-2</v>
-      </c>
-      <c r="H250">
-        <v>21407.916797350001</v>
-      </c>
-      <c r="I250">
-        <v>5.9114087272438047E-2</v>
-      </c>
-      <c r="J250">
-        <v>31594.40712752</v>
-      </c>
-      <c r="K250">
-        <v>5.5577794961617619E-2</v>
-      </c>
-      <c r="L250">
-        <v>6.75</v>
-      </c>
-      <c r="M250">
-        <v>179.26037297873199</v>
-      </c>
-    </row>
-    <row r="251" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A251" s="2">
-        <v>44835</v>
-      </c>
-      <c r="B251">
-        <v>2203.08783657</v>
-      </c>
-      <c r="C251">
-        <v>0.1167990055996227</v>
-      </c>
-      <c r="D251">
-        <v>6579.0635725500006</v>
-      </c>
-      <c r="E251">
-        <v>2.768095673065727E-2</v>
-      </c>
-      <c r="F251">
-        <v>1505.2793700499999</v>
-      </c>
-      <c r="G251">
-        <v>3.9623908097550557E-2</v>
-      </c>
-      <c r="H251">
-        <v>21706.975802270001</v>
-      </c>
-      <c r="I251">
-        <v>6.1310104516475547E-2</v>
-      </c>
-      <c r="J251">
-        <v>31994.406581439998</v>
-      </c>
-      <c r="K251">
-        <v>5.7708391414251957E-2</v>
-      </c>
-      <c r="L251">
-        <v>7</v>
-      </c>
-      <c r="M251">
-        <v>178.96693481014299</v>
-      </c>
-    </row>
-    <row r="252" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A252" s="2">
-        <v>44866</v>
-      </c>
-      <c r="B252">
-        <v>2208.6535991800001</v>
-      </c>
-      <c r="C252">
-        <v>0.112432755178175</v>
-      </c>
-      <c r="D252">
-        <v>6676.3844705000001</v>
-      </c>
-      <c r="E252">
-        <v>2.7402804257062E-2</v>
-      </c>
-      <c r="F252">
-        <v>1508.91184572</v>
-      </c>
-      <c r="G252">
-        <v>3.9345624257904312E-2</v>
-      </c>
-      <c r="H252">
-        <v>22105.60582493</v>
-      </c>
-      <c r="I252">
-        <v>6.4640272972859986E-2</v>
-      </c>
-      <c r="J252">
-        <v>32499.555740330001</v>
-      </c>
-      <c r="K252">
-        <v>5.9608495761184613E-2</v>
-      </c>
-      <c r="L252">
-        <v>7.25</v>
-      </c>
-      <c r="M252">
-        <v>177.723455970728</v>
-      </c>
-    </row>
-    <row r="253" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A253" s="2">
-        <v>44896</v>
-      </c>
-      <c r="B253">
-        <v>2234.6737479899998</v>
-      </c>
-      <c r="C253">
-        <v>0.1029223141037361</v>
-      </c>
-      <c r="D253">
-        <v>6749.00415419</v>
-      </c>
-      <c r="E253">
-        <v>2.541808343879863E-2</v>
-      </c>
-      <c r="F253">
-        <v>1513.8221178900001</v>
-      </c>
-      <c r="G253">
-        <v>3.7173050779859877E-2</v>
-      </c>
-      <c r="H253">
-        <v>22169.33574626</v>
-      </c>
-      <c r="I253">
-        <v>6.4122703935902858E-2</v>
-      </c>
-      <c r="J253">
-        <v>32666.835766330001</v>
-      </c>
-      <c r="K253">
-        <v>5.8746187341576682E-2</v>
-      </c>
-      <c r="L253">
-        <v>7.5</v>
-      </c>
-      <c r="M253">
-        <v>178.01322374453099</v>
       </c>
     </row>
   </sheetData>
@@ -17855,4 +16463,1411 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3852ACBD-58B7-4253-8F1F-B3718FC6AFBC}">
+  <dimension ref="A1:M34"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="2">
+        <v>43891</v>
+      </c>
+      <c r="B1">
+        <v>2159.4283639800001</v>
+      </c>
+      <c r="C1">
+        <v>0.12695874925191039</v>
+      </c>
+      <c r="D1">
+        <v>4956.9658562300001</v>
+      </c>
+      <c r="E1">
+        <v>3.6257077842107473E-2</v>
+      </c>
+      <c r="F1">
+        <v>1443.19440762</v>
+      </c>
+      <c r="G1">
+        <v>3.5151683087284828E-2</v>
+      </c>
+      <c r="H1">
+        <v>14310.29253604</v>
+      </c>
+      <c r="I1">
+        <v>7.6405917177009994E-2</v>
+      </c>
+      <c r="J1">
+        <v>22869.881163869999</v>
+      </c>
+      <c r="K1">
+        <v>6.9744040935945037E-2</v>
+      </c>
+      <c r="L1">
+        <v>1.25</v>
+      </c>
+      <c r="M1">
+        <v>140.82045052103899</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>43922</v>
+      </c>
+      <c r="B2">
+        <v>2138.9006645700001</v>
+      </c>
+      <c r="C2">
+        <v>0.1174060293540956</v>
+      </c>
+      <c r="D2">
+        <v>4833.40990616</v>
+      </c>
+      <c r="E2">
+        <v>3.6674382661831727E-2</v>
+      </c>
+      <c r="F2">
+        <v>1435.3239125</v>
+      </c>
+      <c r="G2">
+        <v>3.6710352026549972E-2</v>
+      </c>
+      <c r="H2">
+        <v>14089.046786409999</v>
+      </c>
+      <c r="I2">
+        <v>7.5415437457299686E-2</v>
+      </c>
+      <c r="J2">
+        <v>22496.681269640001</v>
+      </c>
+      <c r="K2">
+        <v>6.8471206479831084E-2</v>
+      </c>
+      <c r="L2">
+        <v>0.25</v>
+      </c>
+      <c r="M2">
+        <v>104.571783804586</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>43952</v>
+      </c>
+      <c r="B3">
+        <v>2183.1003610900002</v>
+      </c>
+      <c r="C3">
+        <v>0.1124785327905852</v>
+      </c>
+      <c r="D3">
+        <v>4733.6882485699998</v>
+      </c>
+      <c r="E3">
+        <v>3.7745282498055449E-2</v>
+      </c>
+      <c r="F3">
+        <v>1428.6810697999999</v>
+      </c>
+      <c r="G3">
+        <v>3.6032640088950393E-2</v>
+      </c>
+      <c r="H3">
+        <v>14087.11798673</v>
+      </c>
+      <c r="I3">
+        <v>7.4352098866691738E-2</v>
+      </c>
+      <c r="J3">
+        <v>22432.58766619</v>
+      </c>
+      <c r="K3">
+        <v>6.7608514397507119E-2</v>
+      </c>
+      <c r="L3">
+        <v>0.25</v>
+      </c>
+      <c r="M3">
+        <v>116.20409231795</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>43983</v>
+      </c>
+      <c r="B4">
+        <v>2204.0703212399999</v>
+      </c>
+      <c r="C4">
+        <v>0.11094637160779269</v>
+      </c>
+      <c r="D4">
+        <v>4646.4947893199997</v>
+      </c>
+      <c r="E4">
+        <v>3.8160728975217321E-2</v>
+      </c>
+      <c r="F4">
+        <v>1420.3440982899999</v>
+      </c>
+      <c r="G4">
+        <v>3.7407814911870563E-2</v>
+      </c>
+      <c r="H4">
+        <v>14248.5252177</v>
+      </c>
+      <c r="I4">
+        <v>7.426830870131311E-2</v>
+      </c>
+      <c r="J4">
+        <v>22519.43442655</v>
+      </c>
+      <c r="K4">
+        <v>6.8222768015602397E-2</v>
+      </c>
+      <c r="L4">
+        <v>0.25</v>
+      </c>
+      <c r="M4">
+        <v>139.91102445364899</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>44013</v>
+      </c>
+      <c r="B5">
+        <v>2217.3487439099999</v>
+      </c>
+      <c r="C5">
+        <v>0.1156340769146989</v>
+      </c>
+      <c r="D5">
+        <v>4608.5607300699994</v>
+      </c>
+      <c r="E5">
+        <v>3.4936834461017169E-2</v>
+      </c>
+      <c r="F5">
+        <v>1409.0320153600001</v>
+      </c>
+      <c r="G5">
+        <v>3.6914573482356793E-2</v>
+      </c>
+      <c r="H5">
+        <v>14932.27259633</v>
+      </c>
+      <c r="I5">
+        <v>6.6553403465227964E-2</v>
+      </c>
+      <c r="J5">
+        <v>23167.214085669999</v>
+      </c>
+      <c r="K5">
+        <v>6.2919308120480313E-2</v>
+      </c>
+      <c r="L5">
+        <v>0.25</v>
+      </c>
+      <c r="M5">
+        <v>152.544198892754</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>44044</v>
+      </c>
+      <c r="B6">
+        <v>2261.7211269300001</v>
+      </c>
+      <c r="C6">
+        <v>0.11143274656150851</v>
+      </c>
+      <c r="D6">
+        <v>4619.2933561999998</v>
+      </c>
+      <c r="E6">
+        <v>3.2603356746732523E-2</v>
+      </c>
+      <c r="F6">
+        <v>1401.97957561</v>
+      </c>
+      <c r="G6">
+        <v>3.6528284449306427E-2</v>
+      </c>
+      <c r="H6">
+        <v>15448.824612799999</v>
+      </c>
+      <c r="I6">
+        <v>6.2766093787860758E-2</v>
+      </c>
+      <c r="J6">
+        <v>23731.818671540001</v>
+      </c>
+      <c r="K6">
+        <v>6.00026305235625E-2</v>
+      </c>
+      <c r="L6">
+        <v>0.25</v>
+      </c>
+      <c r="M6">
+        <v>156.36406569440399</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>44075</v>
+      </c>
+      <c r="B7">
+        <v>2276.9921576400002</v>
+      </c>
+      <c r="C7">
+        <v>0.11070809773946309</v>
+      </c>
+      <c r="D7">
+        <v>4673.3158472900004</v>
+      </c>
+      <c r="E7">
+        <v>3.0915695022792341E-2</v>
+      </c>
+      <c r="F7">
+        <v>1403.2395340800001</v>
+      </c>
+      <c r="G7">
+        <v>4.1048794386886259E-2</v>
+      </c>
+      <c r="H7">
+        <v>16164.727005320001</v>
+      </c>
+      <c r="I7">
+        <v>6.017986948882903E-2</v>
+      </c>
+      <c r="J7">
+        <v>24518.274544330001</v>
+      </c>
+      <c r="K7">
+        <v>5.864331103308755E-2</v>
+      </c>
+      <c r="L7">
+        <v>0.25</v>
+      </c>
+      <c r="M7">
+        <v>160.26131398211101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>44105</v>
+      </c>
+      <c r="B8">
+        <v>2231.4262205499999</v>
+      </c>
+      <c r="C8">
+        <v>0.10771210436917709</v>
+      </c>
+      <c r="D8">
+        <v>4806.8549881299996</v>
+      </c>
+      <c r="E8">
+        <v>3.1291336042262183E-2</v>
+      </c>
+      <c r="F8">
+        <v>1404.1004755700001</v>
+      </c>
+      <c r="G8">
+        <v>4.3559165860385649E-2</v>
+      </c>
+      <c r="H8">
+        <v>16643.936121160001</v>
+      </c>
+      <c r="I8">
+        <v>5.5730837191919069E-2</v>
+      </c>
+      <c r="J8">
+        <v>25086.317805409999</v>
+      </c>
+      <c r="K8">
+        <v>5.547551112428134E-2</v>
+      </c>
+      <c r="L8">
+        <v>0.25</v>
+      </c>
+      <c r="M8">
+        <v>166.74684518517901</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>44136</v>
+      </c>
+      <c r="B9">
+        <v>2280.1507402299999</v>
+      </c>
+      <c r="C9">
+        <v>0.10319941129693209</v>
+      </c>
+      <c r="D9">
+        <v>4948.6570592999997</v>
+      </c>
+      <c r="E9">
+        <v>3.0511784985431639E-2</v>
+      </c>
+      <c r="F9">
+        <v>1409.1993044200001</v>
+      </c>
+      <c r="G9">
+        <v>4.370211886766949E-2</v>
+      </c>
+      <c r="H9">
+        <v>17039.103716760001</v>
+      </c>
+      <c r="I9">
+        <v>5.5228463543846702E-2</v>
+      </c>
+      <c r="J9">
+        <v>25677.110820710001</v>
+      </c>
+      <c r="K9">
+        <v>5.4646923515431163E-2</v>
+      </c>
+      <c r="L9">
+        <v>0.25</v>
+      </c>
+      <c r="M9">
+        <v>168.292170423214</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>44166</v>
+      </c>
+      <c r="B10">
+        <v>2300.3196402100002</v>
+      </c>
+      <c r="C10">
+        <v>0.101678955690109</v>
+      </c>
+      <c r="D10">
+        <v>5069.7182674599999</v>
+      </c>
+      <c r="E10">
+        <v>2.6994189913548239E-2</v>
+      </c>
+      <c r="F10">
+        <v>1416.1758750700001</v>
+      </c>
+      <c r="G10">
+        <v>4.279667385027601E-2</v>
+      </c>
+      <c r="H10">
+        <v>17303.47789563</v>
+      </c>
+      <c r="I10">
+        <v>5.5811118977760393E-2</v>
+      </c>
+      <c r="J10">
+        <v>26089.69167837</v>
+      </c>
+      <c r="K10">
+        <v>5.4856669325880313E-2</v>
+      </c>
+      <c r="L10">
+        <v>0.25</v>
+      </c>
+      <c r="M10">
+        <v>172.400120770981</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>44197</v>
+      </c>
+      <c r="B11">
+        <v>2275.7306163899998</v>
+      </c>
+      <c r="C11">
+        <v>0.1052414975766867</v>
+      </c>
+      <c r="D11">
+        <v>5112.7377065800001</v>
+      </c>
+      <c r="E11">
+        <v>2.6677292383777761E-2</v>
+      </c>
+      <c r="F11">
+        <v>1409.5821437</v>
+      </c>
+      <c r="G11">
+        <v>4.2525803819176179E-2</v>
+      </c>
+      <c r="H11">
+        <v>17303.545139239999</v>
+      </c>
+      <c r="I11">
+        <v>5.1406725220879752E-2</v>
+      </c>
+      <c r="J11">
+        <v>26101.595605909999</v>
+      </c>
+      <c r="K11">
+        <v>5.0776876665727999E-2</v>
+      </c>
+      <c r="L11">
+        <v>0.25</v>
+      </c>
+      <c r="M11">
+        <v>172.90099314200501</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>44228</v>
+      </c>
+      <c r="B12">
+        <v>2279.78727114</v>
+      </c>
+      <c r="C12">
+        <v>0.1030168990515333</v>
+      </c>
+      <c r="D12">
+        <v>5152.0684472299999</v>
+      </c>
+      <c r="E12">
+        <v>2.6486224526649459E-2</v>
+      </c>
+      <c r="F12">
+        <v>1410.2242385100001</v>
+      </c>
+      <c r="G12">
+        <v>4.2750860993354352E-2</v>
+      </c>
+      <c r="H12">
+        <v>17292.186950200001</v>
+      </c>
+      <c r="I12">
+        <v>5.6515195110583193E-2</v>
+      </c>
+      <c r="J12">
+        <v>26134.26690708</v>
+      </c>
+      <c r="K12">
+        <v>5.3860786025919857E-2</v>
+      </c>
+      <c r="L12">
+        <v>0.25</v>
+      </c>
+      <c r="M12">
+        <v>169.15538756642201</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>44256</v>
+      </c>
+      <c r="B13">
+        <v>2271.0733725499999</v>
+      </c>
+      <c r="C13">
+        <v>9.826505070570403E-2</v>
+      </c>
+      <c r="D13">
+        <v>5229.7713057399997</v>
+      </c>
+      <c r="E13">
+        <v>2.6958617246849309E-2</v>
+      </c>
+      <c r="F13">
+        <v>1410.99503755</v>
+      </c>
+      <c r="G13">
+        <v>4.2955943746791667E-2</v>
+      </c>
+      <c r="H13">
+        <v>17410.84239396</v>
+      </c>
+      <c r="I13">
+        <v>6.1272067265878867E-2</v>
+      </c>
+      <c r="J13">
+        <v>26322.6821098</v>
+      </c>
+      <c r="K13">
+        <v>5.6629337648931077E-2</v>
+      </c>
+      <c r="L13">
+        <v>0.25</v>
+      </c>
+      <c r="M13">
+        <v>168.75683535705301</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>44287</v>
+      </c>
+      <c r="B14">
+        <v>2280.2364451200001</v>
+      </c>
+      <c r="C14">
+        <v>9.9853541937409723E-2</v>
+      </c>
+      <c r="D14">
+        <v>5299.7645609700003</v>
+      </c>
+      <c r="E14">
+        <v>2.8025877446302049E-2</v>
+      </c>
+      <c r="F14">
+        <v>1414.0914274300001</v>
+      </c>
+      <c r="G14">
+        <v>4.3759021969647802E-2</v>
+      </c>
+      <c r="H14">
+        <v>17590.599337340002</v>
+      </c>
+      <c r="I14">
+        <v>6.1999906928981073E-2</v>
+      </c>
+      <c r="J14">
+        <v>26584.691770860001</v>
+      </c>
+      <c r="K14">
+        <v>5.7505229116763812E-2</v>
+      </c>
+      <c r="L14">
+        <v>0.25</v>
+      </c>
+      <c r="M14">
+        <v>167.832160638837</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>44317</v>
+      </c>
+      <c r="B15">
+        <v>2276.4251643399998</v>
+      </c>
+      <c r="C15">
+        <v>9.7517738785127928E-2</v>
+      </c>
+      <c r="D15">
+        <v>5333.5101946000004</v>
+      </c>
+      <c r="E15">
+        <v>3.2891037969255521E-2</v>
+      </c>
+      <c r="F15">
+        <v>1414.1026799700001</v>
+      </c>
+      <c r="G15">
+        <v>4.5129050290289997E-2</v>
+      </c>
+      <c r="H15">
+        <v>17861.444640760001</v>
+      </c>
+      <c r="I15">
+        <v>6.2341615703127802E-2</v>
+      </c>
+      <c r="J15">
+        <v>26885.48267967</v>
+      </c>
+      <c r="K15">
+        <v>5.8441697281614129E-2</v>
+      </c>
+      <c r="L15">
+        <v>0.25</v>
+      </c>
+      <c r="M15">
+        <v>172.46262082341099</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>44348</v>
+      </c>
+      <c r="B16">
+        <v>2286.9315393799998</v>
+      </c>
+      <c r="C16">
+        <v>9.1658109978590793E-2</v>
+      </c>
+      <c r="D16">
+        <v>5358.6517146100005</v>
+      </c>
+      <c r="E16">
+        <v>3.1368390944630307E-2</v>
+      </c>
+      <c r="F16">
+        <v>1408.03971073</v>
+      </c>
+      <c r="G16">
+        <v>4.4266246424034192E-2</v>
+      </c>
+      <c r="H16">
+        <v>18024.676300989999</v>
+      </c>
+      <c r="I16">
+        <v>5.9752386877485048E-2</v>
+      </c>
+      <c r="J16">
+        <v>27078.29926571</v>
+      </c>
+      <c r="K16">
+        <v>5.6260746439557287E-2</v>
+      </c>
+      <c r="L16">
+        <v>0.25</v>
+      </c>
+      <c r="M16">
+        <v>172.756272866323</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>44378</v>
+      </c>
+      <c r="B17">
+        <v>2262.2419197999998</v>
+      </c>
+      <c r="C17">
+        <v>9.8105483802378254E-2</v>
+      </c>
+      <c r="D17">
+        <v>5368.7611469200001</v>
+      </c>
+      <c r="E17">
+        <v>3.2271793767431257E-2</v>
+      </c>
+      <c r="F17">
+        <v>1409.3347980000001</v>
+      </c>
+      <c r="G17">
+        <v>4.3749786947359537E-2</v>
+      </c>
+      <c r="H17">
+        <v>18214.69351021</v>
+      </c>
+      <c r="I17">
+        <v>6.1709936695100623E-2</v>
+      </c>
+      <c r="J17">
+        <v>27255.03137493</v>
+      </c>
+      <c r="K17">
+        <v>5.7844933741875118E-2</v>
+      </c>
+      <c r="L17">
+        <v>0.25</v>
+      </c>
+      <c r="M17">
+        <v>173.54042175974399</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>44409</v>
+      </c>
+      <c r="B18">
+        <v>2234.4294547300001</v>
+      </c>
+      <c r="C18">
+        <v>9.8231403616420049E-2</v>
+      </c>
+      <c r="D18">
+        <v>5406.58861299</v>
+      </c>
+      <c r="E18">
+        <v>3.0962517930030201E-2</v>
+      </c>
+      <c r="F18">
+        <v>1274.8114010700001</v>
+      </c>
+      <c r="G18">
+        <v>3.31111587287116E-2</v>
+      </c>
+      <c r="H18">
+        <v>18427.78186173</v>
+      </c>
+      <c r="I18">
+        <v>5.9889314619637118E-2</v>
+      </c>
+      <c r="J18">
+        <v>27343.611330520002</v>
+      </c>
+      <c r="K18">
+        <v>5.6145973649776762E-2</v>
+      </c>
+      <c r="L18">
+        <v>0.5</v>
+      </c>
+      <c r="M18">
+        <v>174.87920486451901</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>44440</v>
+      </c>
+      <c r="B19">
+        <v>2202.2242701199998</v>
+      </c>
+      <c r="C19">
+        <v>0.1005012039976927</v>
+      </c>
+      <c r="D19">
+        <v>5473.4202434999997</v>
+      </c>
+      <c r="E19">
+        <v>3.062295816570073E-2</v>
+      </c>
+      <c r="F19">
+        <v>1277.1083010699999</v>
+      </c>
+      <c r="G19">
+        <v>3.2102560257145203E-2</v>
+      </c>
+      <c r="H19">
+        <v>18797.73941237</v>
+      </c>
+      <c r="I19">
+        <v>5.9203044509666902E-2</v>
+      </c>
+      <c r="J19">
+        <v>27750.49222706</v>
+      </c>
+      <c r="K19">
+        <v>5.607561073138858E-2</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19">
+        <v>175.854950933071</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>44470</v>
+      </c>
+      <c r="B20">
+        <v>2194.2493606399998</v>
+      </c>
+      <c r="C20">
+        <v>0.1004161101114477</v>
+      </c>
+      <c r="D20">
+        <v>5571.17602627</v>
+      </c>
+      <c r="E20">
+        <v>2.930325374753975E-2</v>
+      </c>
+      <c r="F20">
+        <v>1285.5089196199999</v>
+      </c>
+      <c r="G20">
+        <v>3.1440552673837073E-2</v>
+      </c>
+      <c r="H20">
+        <v>19083.164364209999</v>
+      </c>
+      <c r="I20">
+        <v>5.9528650349525883E-2</v>
+      </c>
+      <c r="J20">
+        <v>28134.098670740001</v>
+      </c>
+      <c r="K20">
+        <v>5.5961465093607811E-2</v>
+      </c>
+      <c r="L20">
+        <v>1.5</v>
+      </c>
+      <c r="M20">
+        <v>175.023326475673</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>44501</v>
+      </c>
+      <c r="B21">
+        <v>2172.2655704700001</v>
+      </c>
+      <c r="C21">
+        <v>9.8535122012585449E-2</v>
+      </c>
+      <c r="D21">
+        <v>5670.17393722</v>
+      </c>
+      <c r="E21">
+        <v>2.8580077620943781E-2</v>
+      </c>
+      <c r="F21">
+        <v>1300.8241159700001</v>
+      </c>
+      <c r="G21">
+        <v>3.1301938325180197E-2</v>
+      </c>
+      <c r="H21">
+        <v>19422.658219389999</v>
+      </c>
+      <c r="I21">
+        <v>6.004569223128834E-2</v>
+      </c>
+      <c r="J21">
+        <v>28565.92184305</v>
+      </c>
+      <c r="K21">
+        <v>5.5962434010417797E-2</v>
+      </c>
+      <c r="L21">
+        <v>2</v>
+      </c>
+      <c r="M21">
+        <v>174.28334484974999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>44531</v>
+      </c>
+      <c r="B22">
+        <v>2169.81716056</v>
+      </c>
+      <c r="C22">
+        <v>9.1217174736012499E-2</v>
+      </c>
+      <c r="D22">
+        <v>5749.7459773599994</v>
+      </c>
+      <c r="E22">
+        <v>2.502358037668688E-2</v>
+      </c>
+      <c r="F22">
+        <v>1388.26564278</v>
+      </c>
+      <c r="G22">
+        <v>2.809212703118107E-2</v>
+      </c>
+      <c r="H22">
+        <v>19628.150631429999</v>
+      </c>
+      <c r="I22">
+        <v>6.021726288427684E-2</v>
+      </c>
+      <c r="J22">
+        <v>28935.97941213</v>
+      </c>
+      <c r="K22">
+        <v>5.5223889091702477E-2</v>
+      </c>
+      <c r="L22">
+        <v>2.5</v>
+      </c>
+      <c r="M22">
+        <v>175.225814954611</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>44562</v>
+      </c>
+      <c r="B23">
+        <v>2163.45077055</v>
+      </c>
+      <c r="C23">
+        <v>9.3923785091879819E-2</v>
+      </c>
+      <c r="D23">
+        <v>5802.8133554100004</v>
+      </c>
+      <c r="E23">
+        <v>2.7455609970888549E-2</v>
+      </c>
+      <c r="F23">
+        <v>1385.66927007</v>
+      </c>
+      <c r="G23">
+        <v>2.9273104979769728E-2</v>
+      </c>
+      <c r="H23">
+        <v>19591.822615789999</v>
+      </c>
+      <c r="I23">
+        <v>5.9054299032267298E-2</v>
+      </c>
+      <c r="J23">
+        <v>28943.756011820002</v>
+      </c>
+      <c r="K23">
+        <v>5.389982758847553E-2</v>
+      </c>
+      <c r="L23">
+        <v>3</v>
+      </c>
+      <c r="M23">
+        <v>177.77595236253299</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>44593</v>
+      </c>
+      <c r="B24">
+        <v>2159.5255895599998</v>
+      </c>
+      <c r="C24">
+        <v>9.7333164277449757E-2</v>
+      </c>
+      <c r="D24">
+        <v>5914.4869055199997</v>
+      </c>
+      <c r="E24">
+        <v>2.795292140822898E-2</v>
+      </c>
+      <c r="F24">
+        <v>1394.5299547</v>
+      </c>
+      <c r="G24">
+        <v>2.907100487398372E-2</v>
+      </c>
+      <c r="H24">
+        <v>19819.768310349999</v>
+      </c>
+      <c r="I24">
+        <v>5.8916916801158348E-2</v>
+      </c>
+      <c r="J24">
+        <v>29288.31076013</v>
+      </c>
+      <c r="K24">
+        <v>5.4057915490261052E-2</v>
+      </c>
+      <c r="L24">
+        <v>3.5</v>
+      </c>
+      <c r="M24">
+        <v>177.45500302739299</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>44621</v>
+      </c>
+      <c r="B25">
+        <v>2154.9887514900001</v>
+      </c>
+      <c r="C25">
+        <v>9.9443574817654645E-2</v>
+      </c>
+      <c r="D25">
+        <v>6025.3310061599996</v>
+      </c>
+      <c r="E25">
+        <v>2.7902767824393208E-2</v>
+      </c>
+      <c r="F25">
+        <v>1402.4647080100001</v>
+      </c>
+      <c r="G25">
+        <v>2.8875945946235711E-2</v>
+      </c>
+      <c r="H25">
+        <v>20139.74479144</v>
+      </c>
+      <c r="I25">
+        <v>5.8641837909758507E-2</v>
+      </c>
+      <c r="J25">
+        <v>29722.529257099999</v>
+      </c>
+      <c r="K25">
+        <v>5.3971710326465507E-2</v>
+      </c>
+      <c r="L25">
+        <v>4</v>
+      </c>
+      <c r="M25">
+        <v>175.624506747689</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>44652</v>
+      </c>
+      <c r="B26">
+        <v>2160.2823818900001</v>
+      </c>
+      <c r="C26">
+        <v>0.10388968486779419</v>
+      </c>
+      <c r="D26">
+        <v>6109.3115564</v>
+      </c>
+      <c r="E26">
+        <v>2.7698388439975741E-2</v>
+      </c>
+      <c r="F26">
+        <v>1409.32815132</v>
+      </c>
+      <c r="G26">
+        <v>2.899783176240598E-2</v>
+      </c>
+      <c r="H26">
+        <v>20322.691519280001</v>
+      </c>
+      <c r="I26">
+        <v>5.7064794004497363E-2</v>
+      </c>
+      <c r="J26">
+        <v>30001.613608889998</v>
+      </c>
+      <c r="K26">
+        <v>5.320409537187834E-2</v>
+      </c>
+      <c r="L26">
+        <v>4.5</v>
+      </c>
+      <c r="M26">
+        <v>175.36384503404199</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>44682</v>
+      </c>
+      <c r="B27">
+        <v>2154.5626099599999</v>
+      </c>
+      <c r="C27">
+        <v>0.1014939018476979</v>
+      </c>
+      <c r="D27">
+        <v>6210.7306745899996</v>
+      </c>
+      <c r="E27">
+        <v>2.7251930952741449E-2</v>
+      </c>
+      <c r="F27">
+        <v>1469.05325739</v>
+      </c>
+      <c r="G27">
+        <v>4.2067353759383641E-2</v>
+      </c>
+      <c r="H27">
+        <v>20483.47195363</v>
+      </c>
+      <c r="I27">
+        <v>5.4972506127947053E-2</v>
+      </c>
+      <c r="J27">
+        <v>30317.818495570002</v>
+      </c>
+      <c r="K27">
+        <v>5.1892990824017937E-2</v>
+      </c>
+      <c r="L27">
+        <v>5</v>
+      </c>
+      <c r="M27">
+        <v>176.549094020246</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>44713</v>
+      </c>
+      <c r="B28">
+        <v>2171.5867223400001</v>
+      </c>
+      <c r="C28">
+        <v>0.1021520059079033</v>
+      </c>
+      <c r="D28">
+        <v>6276.0739399699996</v>
+      </c>
+      <c r="E28">
+        <v>2.6874319215048351E-2</v>
+      </c>
+      <c r="F28">
+        <v>1473.95082613</v>
+      </c>
+      <c r="G28">
+        <v>4.1859331021236047E-2</v>
+      </c>
+      <c r="H28">
+        <v>20658.609303699999</v>
+      </c>
+      <c r="I28">
+        <v>5.5455026776792322E-2</v>
+      </c>
+      <c r="J28">
+        <v>30580.22079214</v>
+      </c>
+      <c r="K28">
+        <v>5.2515106017914599E-2</v>
+      </c>
+      <c r="L28">
+        <v>5.5</v>
+      </c>
+      <c r="M28">
+        <v>179.22937448249701</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>44743</v>
+      </c>
+      <c r="B29">
+        <v>2167.5417105699999</v>
+      </c>
+      <c r="C29">
+        <v>0.1105223508372544</v>
+      </c>
+      <c r="D29">
+        <v>6331.3028230299997</v>
+      </c>
+      <c r="E29">
+        <v>2.7757695861701681E-2</v>
+      </c>
+      <c r="F29">
+        <v>1477.4233848900001</v>
+      </c>
+      <c r="G29">
+        <v>4.1208457787158252E-2</v>
+      </c>
+      <c r="H29">
+        <v>20863.02957418</v>
+      </c>
+      <c r="I29">
+        <v>5.638996804828432E-2</v>
+      </c>
+      <c r="J29">
+        <v>30839.297492670001</v>
+      </c>
+      <c r="K29">
+        <v>5.3458761202114131E-2</v>
+      </c>
+      <c r="L29">
+        <v>6</v>
+      </c>
+      <c r="M29">
+        <v>177.76735736691001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>44774</v>
+      </c>
+      <c r="B30">
+        <v>2183.1975619300001</v>
+      </c>
+      <c r="C30">
+        <v>0.11121653208761929</v>
+      </c>
+      <c r="D30">
+        <v>6404.7049425300002</v>
+      </c>
+      <c r="E30">
+        <v>2.750088030915953E-2</v>
+      </c>
+      <c r="F30">
+        <v>1487.36756025</v>
+      </c>
+      <c r="G30">
+        <v>4.0985748815009493E-2</v>
+      </c>
+      <c r="H30">
+        <v>21115.346774969999</v>
+      </c>
+      <c r="I30">
+        <v>5.7011522646728777E-2</v>
+      </c>
+      <c r="J30">
+        <v>31190.616839679999</v>
+      </c>
+      <c r="K30">
+        <v>5.4082769386895879E-2</v>
+      </c>
+      <c r="L30">
+        <v>6.5</v>
+      </c>
+      <c r="M30">
+        <v>177.59760674853001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>44805</v>
+      </c>
+      <c r="B31">
+        <v>2199.7633651400001</v>
+      </c>
+      <c r="C31">
+        <v>0.10735566742424139</v>
+      </c>
+      <c r="D31">
+        <v>6489.5910629800001</v>
+      </c>
+      <c r="E31">
+        <v>2.7683018923153009E-2</v>
+      </c>
+      <c r="F31">
+        <v>1497.1359020499999</v>
+      </c>
+      <c r="G31">
+        <v>3.972146793659212E-2</v>
+      </c>
+      <c r="H31">
+        <v>21407.916797350001</v>
+      </c>
+      <c r="I31">
+        <v>5.9114087272438047E-2</v>
+      </c>
+      <c r="J31">
+        <v>31594.40712752</v>
+      </c>
+      <c r="K31">
+        <v>5.5577794961617619E-2</v>
+      </c>
+      <c r="L31">
+        <v>6.75</v>
+      </c>
+      <c r="M31">
+        <v>179.26037297873199</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>44835</v>
+      </c>
+      <c r="B32">
+        <v>2203.08783657</v>
+      </c>
+      <c r="C32">
+        <v>0.1167990055996227</v>
+      </c>
+      <c r="D32">
+        <v>6579.0635725500006</v>
+      </c>
+      <c r="E32">
+        <v>2.768095673065727E-2</v>
+      </c>
+      <c r="F32">
+        <v>1505.2793700499999</v>
+      </c>
+      <c r="G32">
+        <v>3.9623908097550557E-2</v>
+      </c>
+      <c r="H32">
+        <v>21706.975802270001</v>
+      </c>
+      <c r="I32">
+        <v>6.1310104516475547E-2</v>
+      </c>
+      <c r="J32">
+        <v>31994.406581439998</v>
+      </c>
+      <c r="K32">
+        <v>5.7708391414251957E-2</v>
+      </c>
+      <c r="L32">
+        <v>7</v>
+      </c>
+      <c r="M32">
+        <v>178.96693481014299</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>44866</v>
+      </c>
+      <c r="B33">
+        <v>2208.6535991800001</v>
+      </c>
+      <c r="C33">
+        <v>0.112432755178175</v>
+      </c>
+      <c r="D33">
+        <v>6676.3844705000001</v>
+      </c>
+      <c r="E33">
+        <v>2.7402804257062E-2</v>
+      </c>
+      <c r="F33">
+        <v>1508.91184572</v>
+      </c>
+      <c r="G33">
+        <v>3.9345624257904312E-2</v>
+      </c>
+      <c r="H33">
+        <v>22105.60582493</v>
+      </c>
+      <c r="I33">
+        <v>6.4640272972859986E-2</v>
+      </c>
+      <c r="J33">
+        <v>32499.555740330001</v>
+      </c>
+      <c r="K33">
+        <v>5.9608495761184613E-2</v>
+      </c>
+      <c r="L33">
+        <v>7.25</v>
+      </c>
+      <c r="M33">
+        <v>177.723455970728</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>44896</v>
+      </c>
+      <c r="B34">
+        <v>2234.6737479899998</v>
+      </c>
+      <c r="C34">
+        <v>0.1029223141037361</v>
+      </c>
+      <c r="D34">
+        <v>6749.00415419</v>
+      </c>
+      <c r="E34">
+        <v>2.541808343879863E-2</v>
+      </c>
+      <c r="F34">
+        <v>1513.8221178900001</v>
+      </c>
+      <c r="G34">
+        <v>3.7173050779859877E-2</v>
+      </c>
+      <c r="H34">
+        <v>22169.33574626</v>
+      </c>
+      <c r="I34">
+        <v>6.4122703935902858E-2</v>
+      </c>
+      <c r="J34">
+        <v>32666.835766330001</v>
+      </c>
+      <c r="K34">
+        <v>5.8746187341576682E-2</v>
+      </c>
+      <c r="L34">
+        <v>7.5</v>
+      </c>
+      <c r="M34">
+        <v>178.01322374453099</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>